--- a/output/전임교원_연구실적_전처리결과.xlsx
+++ b/output/전임교원_연구실적_전처리결과.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,32 +418,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>연도</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>학교명</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>전임교원수</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SCI/SCOPUS논문수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>1인당논문수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>전국순위</t>
         </is>
@@ -3129,11 +3117,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>추계예술대학교</t>
+          <t>금강대학교</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3151,11 +3139,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3173,11 +3161,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3195,11 +3183,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>서울기독대학교</t>
+          <t>목포가톨릭대학교</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3217,11 +3205,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3239,11 +3227,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>목포가톨릭대학교</t>
+          <t>서울기독대학교</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3261,11 +3249,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>금강대학교</t>
+          <t>추계예술대학교</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3290,10 +3278,10 @@
         <v>281</v>
       </c>
       <c r="D130" t="n">
-        <v>311.2127</v>
+        <v>325.9733</v>
       </c>
       <c r="E130" t="n">
-        <v>1.1075</v>
+        <v>1.16</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -3312,10 +3300,10 @@
         <v>1437</v>
       </c>
       <c r="D131" t="n">
-        <v>1187.6728</v>
+        <v>1373.7186</v>
       </c>
       <c r="E131" t="n">
-        <v>0.8265</v>
+        <v>0.956</v>
       </c>
       <c r="F131" t="n">
         <v>2</v>
@@ -3327,17 +3315,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>고려대학교</t>
+          <t>연세대학교</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1449</v>
+        <v>1687</v>
       </c>
       <c r="D132" t="n">
-        <v>1061.4676</v>
+        <v>1446.3592</v>
       </c>
       <c r="E132" t="n">
-        <v>0.7326</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="F132" t="n">
         <v>3</v>
@@ -3349,17 +3337,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>고려대학교</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1687</v>
+        <v>1449</v>
       </c>
       <c r="D133" t="n">
-        <v>1235.4901</v>
+        <v>1157.9638</v>
       </c>
       <c r="E133" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.7991</v>
       </c>
       <c r="F133" t="n">
         <v>4</v>
@@ -3378,10 +3366,10 @@
         <v>1005</v>
       </c>
       <c r="D134" t="n">
-        <v>632.2891</v>
+        <v>704.6642999999999</v>
       </c>
       <c r="E134" t="n">
-        <v>0.6291</v>
+        <v>0.7012</v>
       </c>
       <c r="F134" t="n">
         <v>5</v>
@@ -3400,10 +3388,10 @@
         <v>925</v>
       </c>
       <c r="D135" t="n">
-        <v>571.1994999999999</v>
+        <v>637.3619</v>
       </c>
       <c r="E135" t="n">
-        <v>0.6175</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F135" t="n">
         <v>6</v>
@@ -3415,17 +3403,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>건국대학교</t>
+          <t>경희대학교</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>702</v>
+        <v>1452</v>
       </c>
       <c r="D136" t="n">
-        <v>403.7162</v>
+        <v>950.2813</v>
       </c>
       <c r="E136" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.6545</v>
       </c>
       <c r="F136" t="n">
         <v>7</v>
@@ -3437,17 +3425,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>경희대학교</t>
+          <t>건국대학교</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1452</v>
+        <v>702</v>
       </c>
       <c r="D137" t="n">
-        <v>781.125</v>
+        <v>457.0367</v>
       </c>
       <c r="E137" t="n">
-        <v>0.538</v>
+        <v>0.651</v>
       </c>
       <c r="F137" t="n">
         <v>8</v>
@@ -3459,17 +3447,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>한양대학교(ERICA)</t>
+          <t>중앙대학교</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>389</v>
+        <v>1043</v>
       </c>
       <c r="D138" t="n">
-        <v>204.0329</v>
+        <v>619.0765</v>
       </c>
       <c r="E138" t="n">
-        <v>0.5245</v>
+        <v>0.5936</v>
       </c>
       <c r="F138" t="n">
         <v>9</v>
@@ -3488,10 +3476,10 @@
         <v>1111</v>
       </c>
       <c r="D139" t="n">
-        <v>578.9533</v>
+        <v>657.2491</v>
       </c>
       <c r="E139" t="n">
-        <v>0.5211</v>
+        <v>0.5916</v>
       </c>
       <c r="F139" t="n">
         <v>10</v>
@@ -3503,17 +3491,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>광운대학교</t>
+          <t>가톨릭대학교</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>330</v>
+        <v>1155</v>
       </c>
       <c r="D140" t="n">
-        <v>168.1296</v>
+        <v>654.3594000000001</v>
       </c>
       <c r="E140" t="n">
-        <v>0.5095</v>
+        <v>0.5665</v>
       </c>
       <c r="F140" t="n">
         <v>11</v>
@@ -3525,17 +3513,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>중앙대학교</t>
+          <t>한양대학교(ERICA)</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1043</v>
+        <v>389</v>
       </c>
       <c r="D141" t="n">
-        <v>527.302</v>
+        <v>217.1356</v>
       </c>
       <c r="E141" t="n">
-        <v>0.5056</v>
+        <v>0.5582</v>
       </c>
       <c r="F141" t="n">
         <v>12</v>
@@ -3547,17 +3535,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>인하대학교</t>
+          <t>아주대학교</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>835</v>
+        <v>703</v>
       </c>
       <c r="D142" t="n">
-        <v>369.9814</v>
+        <v>388.6702</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4431</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="F142" t="n">
         <v>13</v>
@@ -3569,17 +3557,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>가톨릭대학교</t>
+          <t>광운대학교</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1155</v>
+        <v>330</v>
       </c>
       <c r="D143" t="n">
-        <v>507.111</v>
+        <v>174.6639</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4391</v>
+        <v>0.5293</v>
       </c>
       <c r="F143" t="n">
         <v>14</v>
@@ -3591,17 +3579,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>아주대학교</t>
+          <t>인하대학교</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>703</v>
+        <v>835</v>
       </c>
       <c r="D144" t="n">
-        <v>307.7049</v>
+        <v>427.8538</v>
       </c>
       <c r="E144" t="n">
-        <v>0.4377</v>
+        <v>0.5124</v>
       </c>
       <c r="F144" t="n">
         <v>15</v>
@@ -3613,17 +3601,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>동국대학교</t>
+          <t>이화여자대학교</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>716</v>
+        <v>997</v>
       </c>
       <c r="D145" t="n">
-        <v>272.6429</v>
+        <v>453.4445</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3808</v>
+        <v>0.4548</v>
       </c>
       <c r="F145" t="n">
         <v>16</v>
@@ -3635,17 +3623,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>숭실대학교</t>
+          <t>동국대학교</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>503</v>
+        <v>716</v>
       </c>
       <c r="D146" t="n">
-        <v>185.373</v>
+        <v>309.1728</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3685</v>
+        <v>0.4318</v>
       </c>
       <c r="F146" t="n">
         <v>17</v>
@@ -3657,17 +3645,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>한국항공대학교</t>
+          <t>건국대학교(글로컬)</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>163</v>
+        <v>483</v>
       </c>
       <c r="D147" t="n">
-        <v>57.7469</v>
+        <v>205.3335</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3543</v>
+        <v>0.4251</v>
       </c>
       <c r="F147" t="n">
         <v>18</v>
@@ -3679,17 +3667,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>건국대학교(글로컬)</t>
+          <t>숭실대학교</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="D148" t="n">
-        <v>153.5799</v>
+        <v>207.7282</v>
       </c>
       <c r="E148" t="n">
-        <v>0.318</v>
+        <v>0.413</v>
       </c>
       <c r="F148" t="n">
         <v>19</v>
@@ -3701,17 +3689,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>한림대학교</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>183</v>
+        <v>803</v>
       </c>
       <c r="D149" t="n">
-        <v>57.3918</v>
+        <v>324.2749</v>
       </c>
       <c r="E149" t="n">
-        <v>0.3136</v>
+        <v>0.4038</v>
       </c>
       <c r="F149" t="n">
         <v>20</v>
@@ -3723,17 +3711,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>한림대학교</t>
+          <t>가천대학교</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>803</v>
+        <v>870</v>
       </c>
       <c r="D150" t="n">
-        <v>251.6849</v>
+        <v>350.0252</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3134</v>
+        <v>0.4023</v>
       </c>
       <c r="F150" t="n">
         <v>21</v>
@@ -3745,17 +3733,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>가천대학교</t>
+          <t>한국항공대학교</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>870</v>
+        <v>163</v>
       </c>
       <c r="D151" t="n">
-        <v>252.2998</v>
+        <v>60.0802</v>
       </c>
       <c r="E151" t="n">
-        <v>0.29</v>
+        <v>0.3686</v>
       </c>
       <c r="F151" t="n">
         <v>22</v>
@@ -3767,17 +3755,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>명지대학교</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>562</v>
+        <v>183</v>
       </c>
       <c r="D152" t="n">
-        <v>143.6696</v>
+        <v>58.2918</v>
       </c>
       <c r="E152" t="n">
-        <v>0.2556</v>
+        <v>0.3185</v>
       </c>
       <c r="F152" t="n">
         <v>23</v>
@@ -3789,17 +3777,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>이화여자대학교</t>
+          <t>차의과학대학교</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>997</v>
+        <v>428</v>
       </c>
       <c r="D153" t="n">
-        <v>249.6217</v>
+        <v>136.1402</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2504</v>
+        <v>0.3181</v>
       </c>
       <c r="F153" t="n">
         <v>24</v>
@@ -3811,17 +3799,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>고려대학교(세종)</t>
+          <t>조선대학교</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>271</v>
+        <v>818</v>
       </c>
       <c r="D154" t="n">
-        <v>67.5172</v>
+        <v>252.3125</v>
       </c>
       <c r="E154" t="n">
-        <v>0.2491</v>
+        <v>0.3085</v>
       </c>
       <c r="F154" t="n">
         <v>25</v>
@@ -3833,17 +3821,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>조선대학교</t>
+          <t>고려대학교(세종)</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>818</v>
+        <v>271</v>
       </c>
       <c r="D155" t="n">
-        <v>202.2195</v>
+        <v>83.2881</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2472</v>
+        <v>0.3073</v>
       </c>
       <c r="F155" t="n">
         <v>26</v>
@@ -3855,17 +3843,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>경기대학교</t>
+          <t>명지대학교</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>513</v>
+        <v>562</v>
       </c>
       <c r="D156" t="n">
-        <v>120.3798</v>
+        <v>165.2003</v>
       </c>
       <c r="E156" t="n">
-        <v>0.2347</v>
+        <v>0.294</v>
       </c>
       <c r="F156" t="n">
         <v>27</v>
@@ -3877,17 +3865,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>선문대학교</t>
+          <t>한서대학교</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>340</v>
+        <v>266</v>
       </c>
       <c r="D157" t="n">
-        <v>78.8456</v>
+        <v>76.48949999999999</v>
       </c>
       <c r="E157" t="n">
-        <v>0.2319</v>
+        <v>0.2876</v>
       </c>
       <c r="F157" t="n">
         <v>28</v>
@@ -3899,17 +3887,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>한서대학교</t>
+          <t>선문대학교</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>266</v>
+        <v>340</v>
       </c>
       <c r="D158" t="n">
-        <v>61.5717</v>
+        <v>95.31180000000001</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2315</v>
+        <v>0.2803</v>
       </c>
       <c r="F158" t="n">
         <v>29</v>
@@ -3928,10 +3916,10 @@
         <v>1106</v>
       </c>
       <c r="D159" t="n">
-        <v>254.1936</v>
+        <v>309.6258</v>
       </c>
       <c r="E159" t="n">
-        <v>0.2298</v>
+        <v>0.28</v>
       </c>
       <c r="F159" t="n">
         <v>30</v>
@@ -3943,17 +3931,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>홍익대학교</t>
+          <t>남서울대학교</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>747</v>
+        <v>349</v>
       </c>
       <c r="D160" t="n">
-        <v>168.1348</v>
+        <v>96.1628</v>
       </c>
       <c r="E160" t="n">
-        <v>0.2251</v>
+        <v>0.2755</v>
       </c>
       <c r="F160" t="n">
         <v>31</v>
@@ -3965,17 +3953,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>차의과학대학교</t>
+          <t>한국외국어대학교</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>428</v>
+        <v>693</v>
       </c>
       <c r="D161" t="n">
-        <v>90.9755</v>
+        <v>187.4919</v>
       </c>
       <c r="E161" t="n">
-        <v>0.2126</v>
+        <v>0.2706</v>
       </c>
       <c r="F161" t="n">
         <v>32</v>
@@ -3987,17 +3975,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>한국외국어대학교</t>
+          <t>경기대학교</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>693</v>
+        <v>513</v>
       </c>
       <c r="D162" t="n">
-        <v>137.7953</v>
+        <v>135.5845</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1988</v>
+        <v>0.2643</v>
       </c>
       <c r="F162" t="n">
         <v>33</v>
@@ -4009,17 +3997,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>순천향대학교</t>
+          <t>홍익대학교</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>900</v>
+        <v>747</v>
       </c>
       <c r="D163" t="n">
-        <v>178.8471</v>
+        <v>190.9705</v>
       </c>
       <c r="E163" t="n">
-        <v>0.1987</v>
+        <v>0.2556</v>
       </c>
       <c r="F163" t="n">
         <v>34</v>
@@ -4031,17 +4019,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>동아대학교</t>
+          <t>순천향대학교</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>832</v>
+        <v>900</v>
       </c>
       <c r="D164" t="n">
-        <v>165.1918</v>
+        <v>228.5747</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1985</v>
+        <v>0.254</v>
       </c>
       <c r="F164" t="n">
         <v>35</v>
@@ -4053,17 +4041,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>계명대학교</t>
+          <t>을지대학교</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>897</v>
+        <v>393</v>
       </c>
       <c r="D165" t="n">
-        <v>167.3748</v>
+        <v>98.5779</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1866</v>
+        <v>0.2508</v>
       </c>
       <c r="F165" t="n">
         <v>36</v>
@@ -4075,17 +4063,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>대구대학교</t>
+          <t>삼육대학교</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>641</v>
+        <v>220</v>
       </c>
       <c r="D166" t="n">
-        <v>118.921</v>
+        <v>54.994</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1855</v>
+        <v>0.25</v>
       </c>
       <c r="F166" t="n">
         <v>37</v>
@@ -4097,17 +4085,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>남서울대학교</t>
+          <t>중원대학교</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>349</v>
+        <v>158</v>
       </c>
       <c r="D167" t="n">
-        <v>64.69370000000001</v>
+        <v>39.1305</v>
       </c>
       <c r="E167" t="n">
-        <v>0.1854</v>
+        <v>0.2477</v>
       </c>
       <c r="F167" t="n">
         <v>38</v>
@@ -4119,17 +4107,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>대구가톨릭대학교</t>
+          <t>동아대학교</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>644</v>
+        <v>832</v>
       </c>
       <c r="D168" t="n">
-        <v>115.8482</v>
+        <v>199.9913</v>
       </c>
       <c r="E168" t="n">
-        <v>0.1799</v>
+        <v>0.2404</v>
       </c>
       <c r="F168" t="n">
         <v>39</v>
@@ -4141,17 +4129,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>중원대학교</t>
+          <t>인제대학교</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>158</v>
+        <v>994</v>
       </c>
       <c r="D169" t="n">
-        <v>28.3797</v>
+        <v>235.1166</v>
       </c>
       <c r="E169" t="n">
-        <v>0.1796</v>
+        <v>0.2365</v>
       </c>
       <c r="F169" t="n">
         <v>40</v>
@@ -4163,17 +4151,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>인제대학교</t>
+          <t>숙명여자대학교</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>994</v>
+        <v>464</v>
       </c>
       <c r="D170" t="n">
-        <v>177.1874</v>
+        <v>108.2322</v>
       </c>
       <c r="E170" t="n">
-        <v>0.1783</v>
+        <v>0.2333</v>
       </c>
       <c r="F170" t="n">
         <v>41</v>
@@ -4185,17 +4173,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>국민대학교</t>
+          <t>대구가톨릭대학교</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D171" t="n">
-        <v>113.3836</v>
+        <v>149.6194</v>
       </c>
       <c r="E171" t="n">
-        <v>0.175</v>
+        <v>0.2323</v>
       </c>
       <c r="F171" t="n">
         <v>42</v>
@@ -4207,17 +4195,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>삼육대학교</t>
+          <t>계명대학교</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>220</v>
+        <v>897</v>
       </c>
       <c r="D172" t="n">
-        <v>38.0604</v>
+        <v>207.9418</v>
       </c>
       <c r="E172" t="n">
-        <v>0.173</v>
+        <v>0.2318</v>
       </c>
       <c r="F172" t="n">
         <v>43</v>
@@ -4229,17 +4217,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>부산가톨릭대학교</t>
+          <t>대구대학교</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>148</v>
+        <v>641</v>
       </c>
       <c r="D173" t="n">
-        <v>23.6801</v>
+        <v>139.4586</v>
       </c>
       <c r="E173" t="n">
-        <v>0.16</v>
+        <v>0.2176</v>
       </c>
       <c r="F173" t="n">
         <v>44</v>
@@ -4251,17 +4239,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>을지대학교</t>
+          <t>부산가톨릭대학교</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>393</v>
+        <v>148</v>
       </c>
       <c r="D174" t="n">
-        <v>62.2359</v>
+        <v>31.1409</v>
       </c>
       <c r="E174" t="n">
-        <v>0.1584</v>
+        <v>0.2104</v>
       </c>
       <c r="F174" t="n">
         <v>45</v>
@@ -4273,17 +4261,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>청주대학교</t>
+          <t>국민대학교</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>405</v>
+        <v>648</v>
       </c>
       <c r="D175" t="n">
-        <v>63.4454</v>
+        <v>133.5011</v>
       </c>
       <c r="E175" t="n">
-        <v>0.1567</v>
+        <v>0.206</v>
       </c>
       <c r="F175" t="n">
         <v>46</v>
@@ -4302,10 +4290,10 @@
         <v>429</v>
       </c>
       <c r="D176" t="n">
-        <v>67.0309</v>
+        <v>86.78700000000001</v>
       </c>
       <c r="E176" t="n">
-        <v>0.1562</v>
+        <v>0.2023</v>
       </c>
       <c r="F176" t="n">
         <v>47</v>
@@ -4317,17 +4305,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>숙명여자대학교</t>
+          <t>청주대학교</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>464</v>
+        <v>405</v>
       </c>
       <c r="D177" t="n">
-        <v>72.1692</v>
+        <v>78.92319999999999</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1555</v>
+        <v>0.1949</v>
       </c>
       <c r="F177" t="n">
         <v>48</v>
@@ -4346,10 +4334,10 @@
         <v>286</v>
       </c>
       <c r="D178" t="n">
-        <v>37.7952</v>
+        <v>54.5225</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1322</v>
+        <v>0.1906</v>
       </c>
       <c r="F178" t="n">
         <v>49</v>
@@ -4361,17 +4349,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>경일대학교</t>
+          <t>덕성여자대학교</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="D179" t="n">
-        <v>32.8451</v>
+        <v>35.9768</v>
       </c>
       <c r="E179" t="n">
-        <v>0.1293</v>
+        <v>0.1845</v>
       </c>
       <c r="F179" t="n">
         <v>50</v>
@@ -4390,10 +4378,10 @@
         <v>477</v>
       </c>
       <c r="D180" t="n">
-        <v>61.4167</v>
+        <v>77.3614</v>
       </c>
       <c r="E180" t="n">
-        <v>0.1288</v>
+        <v>0.1622</v>
       </c>
       <c r="F180" t="n">
         <v>51</v>
@@ -4405,17 +4393,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>한성대학교</t>
+          <t>경일대학교</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D181" t="n">
-        <v>32.2249</v>
+        <v>40.79510000000001</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1254</v>
+        <v>0.1606</v>
       </c>
       <c r="F181" t="n">
         <v>52</v>
@@ -4427,17 +4415,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>원광대학교</t>
+          <t>고신대학교</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>753</v>
+        <v>314</v>
       </c>
       <c r="D182" t="n">
-        <v>88.2385</v>
+        <v>49.1983</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1172</v>
+        <v>0.1567</v>
       </c>
       <c r="F182" t="n">
         <v>53</v>
@@ -4449,17 +4437,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>상명대학교</t>
+          <t>전주대학교</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>475</v>
+        <v>380</v>
       </c>
       <c r="D183" t="n">
-        <v>52.28529999999999</v>
+        <v>59.0145</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1101</v>
+        <v>0.1553</v>
       </c>
       <c r="F183" t="n">
         <v>54</v>
@@ -4471,17 +4459,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>우송대학교</t>
+          <t>원광대학교</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>332</v>
+        <v>753</v>
       </c>
       <c r="D184" t="n">
-        <v>34.3871</v>
+        <v>114.1152</v>
       </c>
       <c r="E184" t="n">
-        <v>0.1036</v>
+        <v>0.1515</v>
       </c>
       <c r="F184" t="n">
         <v>55</v>
@@ -4493,17 +4481,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>고신대학교</t>
+          <t>성신여자대학교</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="D185" t="n">
-        <v>32.407</v>
+        <v>50.1347</v>
       </c>
       <c r="E185" t="n">
-        <v>0.1032</v>
+        <v>0.1506</v>
       </c>
       <c r="F185" t="n">
         <v>56</v>
@@ -4515,17 +4503,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>성결대학교</t>
+          <t>가톨릭관동대학교</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>202</v>
+        <v>508</v>
       </c>
       <c r="D186" t="n">
-        <v>20.8036</v>
+        <v>72.7248</v>
       </c>
       <c r="E186" t="n">
-        <v>0.103</v>
+        <v>0.1432</v>
       </c>
       <c r="F186" t="n">
         <v>57</v>
@@ -4537,20 +4525,20 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>경남대학교</t>
+          <t>건양대학교</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>456</v>
+        <v>396</v>
       </c>
       <c r="D187" t="n">
-        <v>46.2462</v>
+        <v>56.72340000000001</v>
       </c>
       <c r="E187" t="n">
-        <v>0.1014</v>
+        <v>0.1432</v>
       </c>
       <c r="F187" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="188">
@@ -4559,17 +4547,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>가톨릭관동대학교</t>
+          <t>서울여자대학교</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>508</v>
+        <v>241</v>
       </c>
       <c r="D188" t="n">
-        <v>50.9596</v>
+        <v>34.1238</v>
       </c>
       <c r="E188" t="n">
-        <v>0.1003</v>
+        <v>0.1416</v>
       </c>
       <c r="F188" t="n">
         <v>59</v>
@@ -4581,17 +4569,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>중부대학교</t>
+          <t>상명대학교</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>292</v>
+        <v>475</v>
       </c>
       <c r="D189" t="n">
-        <v>29.1306</v>
+        <v>65.25829999999999</v>
       </c>
       <c r="E189" t="n">
-        <v>0.0998</v>
+        <v>0.1374</v>
       </c>
       <c r="F189" t="n">
         <v>60</v>
@@ -4603,17 +4591,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>세한대학교</t>
+          <t>경남대학교</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>146</v>
+        <v>456</v>
       </c>
       <c r="D190" t="n">
-        <v>14.481</v>
+        <v>62.1075</v>
       </c>
       <c r="E190" t="n">
-        <v>0.0992</v>
+        <v>0.1362</v>
       </c>
       <c r="F190" t="n">
         <v>61</v>
@@ -4625,17 +4613,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>대구한의대학교</t>
+          <t>한성대학교</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D191" t="n">
-        <v>25.759</v>
+        <v>33.7011</v>
       </c>
       <c r="E191" t="n">
-        <v>0.0983</v>
+        <v>0.1311</v>
       </c>
       <c r="F191" t="n">
         <v>62</v>
@@ -4647,17 +4635,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>건양대학교</t>
+          <t>경동대학교</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>396</v>
+        <v>246</v>
       </c>
       <c r="D192" t="n">
-        <v>37.9908</v>
+        <v>31.8065</v>
       </c>
       <c r="E192" t="n">
-        <v>0.0959</v>
+        <v>0.1293</v>
       </c>
       <c r="F192" t="n">
         <v>63</v>
@@ -4669,17 +4657,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>서울여자대학교</t>
+          <t>서원대학교</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="D193" t="n">
-        <v>22.9832</v>
+        <v>32.2172</v>
       </c>
       <c r="E193" t="n">
-        <v>0.0954</v>
+        <v>0.1284</v>
       </c>
       <c r="F193" t="n">
         <v>64</v>
@@ -4691,17 +4679,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>덕성여자대학교</t>
+          <t>우송대학교</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>195</v>
+        <v>332</v>
       </c>
       <c r="D194" t="n">
-        <v>18.1498</v>
+        <v>42.4288</v>
       </c>
       <c r="E194" t="n">
-        <v>0.0931</v>
+        <v>0.1278</v>
       </c>
       <c r="F194" t="n">
         <v>65</v>
@@ -4713,17 +4701,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>극동대학교</t>
+          <t>세한대학교</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D195" t="n">
-        <v>13.6222</v>
+        <v>18.0921</v>
       </c>
       <c r="E195" t="n">
-        <v>0.0927</v>
+        <v>0.1239</v>
       </c>
       <c r="F195" t="n">
         <v>66</v>
@@ -4735,17 +4723,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>김천대학교</t>
+          <t>극동대학교</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D196" t="n">
-        <v>13.8609</v>
+        <v>17.8985</v>
       </c>
       <c r="E196" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1218</v>
       </c>
       <c r="F196" t="n">
         <v>67</v>
@@ -4757,17 +4745,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>성신여자대학교</t>
+          <t>중부대학교</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>333</v>
+        <v>292</v>
       </c>
       <c r="D197" t="n">
-        <v>29.4283</v>
+        <v>35.2568</v>
       </c>
       <c r="E197" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1207</v>
       </c>
       <c r="F197" t="n">
         <v>68</v>
@@ -4779,17 +4767,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>목원대학교</t>
+          <t>대구한의대학교</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="D198" t="n">
-        <v>26.0452</v>
+        <v>31.3541</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0871</v>
+        <v>0.1197</v>
       </c>
       <c r="F198" t="n">
         <v>69</v>
@@ -4801,17 +4789,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>한동대학교</t>
+          <t>동명대학교</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>149</v>
+        <v>281</v>
       </c>
       <c r="D199" t="n">
-        <v>12.8854</v>
+        <v>32.0051</v>
       </c>
       <c r="E199" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.1139</v>
       </c>
       <c r="F199" t="n">
         <v>70</v>
@@ -4823,17 +4811,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>전주대학교</t>
+          <t>목원대학교</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>380</v>
+        <v>299</v>
       </c>
       <c r="D200" t="n">
-        <v>30.2026</v>
+        <v>33.7118</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0795</v>
+        <v>0.1127</v>
       </c>
       <c r="F200" t="n">
         <v>71</v>
@@ -4845,17 +4833,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>위덕대학교</t>
+          <t>김천대학교</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="D201" t="n">
-        <v>10.3352</v>
+        <v>17.2021</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0789</v>
+        <v>0.1103</v>
       </c>
       <c r="F201" t="n">
         <v>72</v>
@@ -4867,17 +4855,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>경동대학교</t>
+          <t>배재대학교</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>246</v>
+        <v>324</v>
       </c>
       <c r="D202" t="n">
-        <v>19.0256</v>
+        <v>34.6495</v>
       </c>
       <c r="E202" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1069</v>
       </c>
       <c r="F202" t="n">
         <v>73</v>
@@ -4889,17 +4877,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>신라대학교</t>
+          <t>성결대학교</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>349</v>
+        <v>202</v>
       </c>
       <c r="D203" t="n">
-        <v>26.4147</v>
+        <v>21.5036</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0757</v>
+        <v>0.1065</v>
       </c>
       <c r="F203" t="n">
         <v>74</v>
@@ -4911,17 +4899,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>배재대학교</t>
+          <t>신라대학교</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="D204" t="n">
-        <v>23.984</v>
+        <v>35.8491</v>
       </c>
       <c r="E204" t="n">
-        <v>0.074</v>
+        <v>0.1027</v>
       </c>
       <c r="F204" t="n">
         <v>75</v>
@@ -4933,17 +4921,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>서원대학교</t>
+          <t>한동대학교</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>251</v>
+        <v>149</v>
       </c>
       <c r="D205" t="n">
-        <v>18.5172</v>
+        <v>15.0632</v>
       </c>
       <c r="E205" t="n">
-        <v>0.0738</v>
+        <v>0.1011</v>
       </c>
       <c r="F205" t="n">
         <v>76</v>
@@ -4955,17 +4943,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>동신대학교</t>
+          <t>예수대학교</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>281</v>
+        <v>23</v>
       </c>
       <c r="D206" t="n">
-        <v>20.7176</v>
+        <v>2.2667</v>
       </c>
       <c r="E206" t="n">
-        <v>0.0737</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F206" t="n">
         <v>77</v>
@@ -4977,17 +4965,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>동명대학교</t>
+          <t>대전대학교</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="D207" t="n">
-        <v>19.4132</v>
+        <v>33.9757</v>
       </c>
       <c r="E207" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0941</v>
       </c>
       <c r="F207" t="n">
         <v>78</v>
@@ -4999,17 +4987,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>경성대학교</t>
+          <t>동신대학교</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>451</v>
+        <v>281</v>
       </c>
       <c r="D208" t="n">
-        <v>30.298</v>
+        <v>24.5223</v>
       </c>
       <c r="E208" t="n">
-        <v>0.0672</v>
+        <v>0.0873</v>
       </c>
       <c r="F208" t="n">
         <v>79</v>
@@ -5021,20 +5009,20 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>수원대학교</t>
+          <t>유원대학교</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>400</v>
+        <v>139</v>
       </c>
       <c r="D209" t="n">
-        <v>26.5629</v>
+        <v>12.128</v>
       </c>
       <c r="E209" t="n">
-        <v>0.0664</v>
+        <v>0.0873</v>
       </c>
       <c r="F209" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="210">
@@ -5043,17 +5031,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>대전대학교</t>
+          <t>수원대학교</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="D210" t="n">
-        <v>23.9071</v>
+        <v>34.4945</v>
       </c>
       <c r="E210" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0862</v>
       </c>
       <c r="F210" t="n">
         <v>81</v>
@@ -5065,17 +5053,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>서경대학교</t>
+          <t>동덕여자대학교</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D211" t="n">
-        <v>14.6334</v>
+        <v>19.8556</v>
       </c>
       <c r="E211" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0834</v>
       </c>
       <c r="F211" t="n">
         <v>82</v>
@@ -5087,17 +5075,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>유원대학교</t>
+          <t>성공회대학교</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="D212" t="n">
-        <v>9.0914</v>
+        <v>6.719</v>
       </c>
       <c r="E212" t="n">
-        <v>0.0654</v>
+        <v>0.081</v>
       </c>
       <c r="F212" t="n">
         <v>83</v>
@@ -5109,17 +5097,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>동덕여자대학교</t>
+          <t>위덕대학교</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>238</v>
+        <v>131</v>
       </c>
       <c r="D213" t="n">
-        <v>15.0331</v>
+        <v>10.3352</v>
       </c>
       <c r="E213" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0789</v>
       </c>
       <c r="F213" t="n">
         <v>84</v>
@@ -5138,10 +5126,10 @@
         <v>123</v>
       </c>
       <c r="D214" t="n">
-        <v>7.7141</v>
+        <v>9.657</v>
       </c>
       <c r="E214" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0785</v>
       </c>
       <c r="F214" t="n">
         <v>85</v>
@@ -5160,10 +5148,10 @@
         <v>202</v>
       </c>
       <c r="D215" t="n">
-        <v>12.5873</v>
+        <v>15.704</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0623</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="F215" t="n">
         <v>86</v>
@@ -5175,17 +5163,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>한신대학교</t>
+          <t>경성대학교</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>170</v>
+        <v>451</v>
       </c>
       <c r="D216" t="n">
-        <v>10.2</v>
+        <v>34.6904</v>
       </c>
       <c r="E216" t="n">
-        <v>0.06</v>
+        <v>0.0769</v>
       </c>
       <c r="F216" t="n">
         <v>87</v>
@@ -5197,17 +5185,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>동의대학교</t>
+          <t>우석대학교</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>583</v>
+        <v>266</v>
       </c>
       <c r="D217" t="n">
-        <v>34.9256</v>
+        <v>20.287</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0599</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F217" t="n">
         <v>88</v>
@@ -5219,17 +5207,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>성공회대학교</t>
+          <t>동서대학교</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="D218" t="n">
-        <v>4.719</v>
+        <v>26.5541</v>
       </c>
       <c r="E218" t="n">
-        <v>0.0569</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="F218" t="n">
         <v>89</v>
@@ -5241,17 +5229,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>대진대학교</t>
+          <t>백석대학교</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>272</v>
+        <v>499</v>
       </c>
       <c r="D219" t="n">
-        <v>14.7551</v>
+        <v>36.8491</v>
       </c>
       <c r="E219" t="n">
-        <v>0.0542</v>
+        <v>0.0738</v>
       </c>
       <c r="F219" t="n">
         <v>90</v>
@@ -5263,17 +5251,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>우석대학교</t>
+          <t>동의대학교</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>266</v>
+        <v>583</v>
       </c>
       <c r="D220" t="n">
-        <v>14.0343</v>
+        <v>41.9412</v>
       </c>
       <c r="E220" t="n">
-        <v>0.0528</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F220" t="n">
         <v>91</v>
@@ -5285,17 +5273,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>동서대학교</t>
+          <t>한국성서대학교</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>357</v>
+        <v>46</v>
       </c>
       <c r="D221" t="n">
-        <v>17.5383</v>
+        <v>3.1749</v>
       </c>
       <c r="E221" t="n">
-        <v>0.0491</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F221" t="n">
         <v>92</v>
@@ -5307,17 +5295,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>광주대학교</t>
+          <t>한신대학교</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="D222" t="n">
-        <v>11.3014</v>
+        <v>11.4</v>
       </c>
       <c r="E222" t="n">
-        <v>0.0448</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="F222" t="n">
         <v>93</v>
@@ -5329,17 +5317,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>영산대학교</t>
+          <t>광주여자대학교</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="D223" t="n">
-        <v>10.1512</v>
+        <v>8.7906</v>
       </c>
       <c r="E223" t="n">
-        <v>0.0406</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F223" t="n">
         <v>94</v>
@@ -5351,20 +5339,20 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>가야대학교</t>
+          <t>대진대학교</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="D224" t="n">
-        <v>3.4</v>
+        <v>18.104</v>
       </c>
       <c r="E224" t="n">
-        <v>0.0358</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F224" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="225">
@@ -5373,17 +5361,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>동양대학교</t>
+          <t>서경대학교</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>159</v>
+        <v>223</v>
       </c>
       <c r="D225" t="n">
-        <v>5.544</v>
+        <v>14.8001</v>
       </c>
       <c r="E225" t="n">
-        <v>0.0349</v>
+        <v>0.0664</v>
       </c>
       <c r="F225" t="n">
         <v>96</v>
@@ -5395,20 +5383,20 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>용인대학교</t>
+          <t>영산대학교</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D226" t="n">
-        <v>8.212999999999999</v>
+        <v>16.0151</v>
       </c>
       <c r="E226" t="n">
-        <v>0.0349</v>
+        <v>0.0641</v>
       </c>
       <c r="F226" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="227">
@@ -5417,17 +5405,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>예원예술대학교</t>
+          <t>용인대학교</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="D227" t="n">
-        <v>2.75</v>
+        <v>14.8846</v>
       </c>
       <c r="E227" t="n">
-        <v>0.0344</v>
+        <v>0.0633</v>
       </c>
       <c r="F227" t="n">
         <v>98</v>
@@ -5439,17 +5427,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>한세대학교</t>
+          <t>강남대학교</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>132</v>
+        <v>241</v>
       </c>
       <c r="D228" t="n">
-        <v>4.5</v>
+        <v>14.7659</v>
       </c>
       <c r="E228" t="n">
-        <v>0.0341</v>
+        <v>0.0613</v>
       </c>
       <c r="F228" t="n">
         <v>99</v>
@@ -5461,17 +5449,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>신한대학교</t>
+          <t>광주대학교</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="D229" t="n">
-        <v>6.7346</v>
+        <v>15.282</v>
       </c>
       <c r="E229" t="n">
-        <v>0.0335</v>
+        <v>0.0606</v>
       </c>
       <c r="F229" t="n">
         <v>100</v>
@@ -5483,17 +5471,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>한라대학교</t>
+          <t>신한대학교</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="D230" t="n">
-        <v>4.3584</v>
+        <v>12.0157</v>
       </c>
       <c r="E230" t="n">
-        <v>0.0323</v>
+        <v>0.0598</v>
       </c>
       <c r="F230" t="n">
         <v>101</v>
@@ -5505,17 +5493,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>백석대학교</t>
+          <t>동양대학교</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>499</v>
+        <v>159</v>
       </c>
       <c r="D231" t="n">
-        <v>15.6537</v>
+        <v>8.487299999999999</v>
       </c>
       <c r="E231" t="n">
-        <v>0.0314</v>
+        <v>0.0534</v>
       </c>
       <c r="F231" t="n">
         <v>102</v>
@@ -5527,17 +5515,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>서울기독대학교</t>
+          <t>가야대학교</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="D232" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0303</v>
+        <v>0.0526</v>
       </c>
       <c r="F232" t="n">
         <v>103</v>
@@ -5549,17 +5537,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>상지대학교</t>
+          <t>나사렛대학교</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>275</v>
+        <v>193</v>
       </c>
       <c r="D233" t="n">
-        <v>8.3154</v>
+        <v>8.898199999999999</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0302</v>
+        <v>0.0461</v>
       </c>
       <c r="F233" t="n">
         <v>104</v>
@@ -5571,17 +5559,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>나사렛대학교</t>
+          <t>한세대학교</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="D234" t="n">
-        <v>5.6394</v>
+        <v>6</v>
       </c>
       <c r="E234" t="n">
-        <v>0.0292</v>
+        <v>0.0455</v>
       </c>
       <c r="F234" t="n">
         <v>105</v>
@@ -5593,17 +5581,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>강남대학교</t>
+          <t>상지대학교</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="D235" t="n">
-        <v>6.2333</v>
+        <v>12.0688</v>
       </c>
       <c r="E235" t="n">
-        <v>0.0259</v>
+        <v>0.0439</v>
       </c>
       <c r="F235" t="n">
         <v>106</v>
@@ -5615,17 +5603,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>창신대학교</t>
+          <t>협성대학교</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="D236" t="n">
-        <v>1.8953</v>
+        <v>6.666600000000001</v>
       </c>
       <c r="E236" t="n">
-        <v>0.0231</v>
+        <v>0.0409</v>
       </c>
       <c r="F236" t="n">
         <v>107</v>
@@ -5644,10 +5632,10 @@
         <v>108</v>
       </c>
       <c r="D237" t="n">
-        <v>2.4096</v>
+        <v>3.8429</v>
       </c>
       <c r="E237" t="n">
-        <v>0.0223</v>
+        <v>0.0356</v>
       </c>
       <c r="F237" t="n">
         <v>108</v>
@@ -5659,17 +5647,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>광주여자대학교</t>
+          <t>창신대학교</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="D238" t="n">
-        <v>2.8858</v>
+        <v>2.8953</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0219</v>
+        <v>0.0353</v>
       </c>
       <c r="F238" t="n">
         <v>109</v>
@@ -5681,17 +5669,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>경운대학교</t>
+          <t>예원예술대학교</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="D239" t="n">
-        <v>3.5611</v>
+        <v>2.75</v>
       </c>
       <c r="E239" t="n">
-        <v>0.017</v>
+        <v>0.0344</v>
       </c>
       <c r="F239" t="n">
         <v>110</v>
@@ -5703,17 +5691,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>부산외국어대학교</t>
+          <t>한라대학교</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="D240" t="n">
-        <v>3.8667</v>
+        <v>4.3584</v>
       </c>
       <c r="E240" t="n">
-        <v>0.0133</v>
+        <v>0.0323</v>
       </c>
       <c r="F240" t="n">
         <v>111</v>
@@ -5725,17 +5713,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>협성대학교</t>
+          <t>경운대학교</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="D241" t="n">
-        <v>1.6</v>
+        <v>6.5651</v>
       </c>
       <c r="E241" t="n">
-        <v>0.0098</v>
+        <v>0.0313</v>
       </c>
       <c r="F241" t="n">
         <v>112</v>
@@ -5747,17 +5735,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>한일장신대학교</t>
+          <t>서울기독대학교</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D242" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0.0089</v>
+        <v>0.0303</v>
       </c>
       <c r="F242" t="n">
         <v>113</v>
@@ -5769,17 +5757,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>금강대학교</t>
+          <t>총신대학교</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="D243" t="n">
-        <v>0.25</v>
+        <v>3.4333</v>
       </c>
       <c r="E243" t="n">
-        <v>0.0083</v>
+        <v>0.0272</v>
       </c>
       <c r="F243" t="n">
         <v>114</v>
@@ -5791,17 +5779,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>총신대학교</t>
+          <t>부산외국어대학교</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>126</v>
+        <v>290</v>
       </c>
       <c r="D244" t="n">
-        <v>1</v>
+        <v>4.3667</v>
       </c>
       <c r="E244" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0151</v>
       </c>
       <c r="F244" t="n">
         <v>115</v>
@@ -5813,17 +5801,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>제주국제대학교</t>
+          <t>평택대학교</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="D245" t="n">
-        <v>0.2666</v>
+        <v>1.6291</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0031</v>
+        <v>0.0098</v>
       </c>
       <c r="F245" t="n">
         <v>116</v>
@@ -5835,17 +5823,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>평택대학교</t>
+          <t>한일장신대학교</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="D246" t="n">
-        <v>0.4028</v>
+        <v>0.4</v>
       </c>
       <c r="E246" t="n">
-        <v>0.0024</v>
+        <v>0.0089</v>
       </c>
       <c r="F246" t="n">
         <v>117</v>
@@ -5857,17 +5845,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>신경주대학교</t>
+          <t>인천가톨릭대학교</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="D247" t="n">
-        <v>0.1667</v>
+        <v>0.4102</v>
       </c>
       <c r="E247" t="n">
-        <v>0.0017</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F247" t="n">
         <v>118</v>
@@ -5879,17 +5867,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>대구예술대학교</t>
+          <t>금강대학교</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E248" t="n">
-        <v>0</v>
+        <v>0.0083</v>
       </c>
       <c r="F248" t="n">
         <v>119</v>
@@ -5901,20 +5889,20 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>서울신학대학교</t>
+          <t>제주국제대학교</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>0.4666</v>
       </c>
       <c r="E249" t="n">
-        <v>0</v>
+        <v>0.0054</v>
       </c>
       <c r="F249" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="250">
@@ -5923,20 +5911,20 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>목포가톨릭대학교</t>
+          <t>신경주대학교</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="D250" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="E250" t="n">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="F250" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="251">
@@ -5945,11 +5933,11 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>대구예술대학교</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D251" t="n">
         <v>0</v>
@@ -5958,7 +5946,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="252">
@@ -5967,11 +5955,11 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>인천가톨릭대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
@@ -5980,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="253">
@@ -5989,11 +5977,11 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>예수대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -6002,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="254">
@@ -6011,11 +5999,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>추계예술대학교</t>
+          <t>목포가톨릭대학교</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D254" t="n">
         <v>0</v>
@@ -6024,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="F254" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="255">
@@ -6033,11 +6021,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D255" t="n">
         <v>0</v>
@@ -6046,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="256">
@@ -6055,11 +6043,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>서울신학대학교</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -6068,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="257">
@@ -6077,11 +6065,11 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>한국성서대학교</t>
+          <t>추계예술대학교</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -6090,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="258">
@@ -8783,11 +8771,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>추계예술대학교</t>
+          <t>대구예술대학교</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D380" t="n">
         <v>0</v>
@@ -8805,11 +8793,11 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>대구예술대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D381" t="n">
         <v>0</v>
@@ -8849,11 +8837,11 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>서울기독대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D383" t="n">
         <v>0</v>
@@ -8871,11 +8859,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>서울기독대학교</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D384" t="n">
         <v>0</v>
@@ -8893,11 +8881,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>추계예술대학교</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D385" t="n">
         <v>0</v>
@@ -10499,14 +10487,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>목원대학교</t>
+          <t>동덕여자대학교</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="D458" t="n">
-        <v>32.0942</v>
+        <v>26.2845</v>
       </c>
       <c r="E458" t="n">
         <v>0.1138</v>
@@ -10521,14 +10509,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>동덕여자대학교</t>
+          <t>목원대학교</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>231</v>
+        <v>282</v>
       </c>
       <c r="D459" t="n">
-        <v>26.2845</v>
+        <v>32.0942</v>
       </c>
       <c r="E459" t="n">
         <v>0.1138</v>
@@ -10961,14 +10949,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>한라대학교</t>
+          <t>신한대학교</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="D479" t="n">
-        <v>8.1006</v>
+        <v>15.1899</v>
       </c>
       <c r="E479" t="n">
         <v>0.0669</v>
@@ -10983,14 +10971,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>신한대학교</t>
+          <t>한라대학교</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="D480" t="n">
-        <v>15.1899</v>
+        <v>8.1006</v>
       </c>
       <c r="E480" t="n">
         <v>0.0669</v>
@@ -11599,11 +11587,11 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>금강대학교</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D508" t="n">
         <v>0</v>
@@ -11621,11 +11609,11 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>대구예술대학교</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D509" t="n">
         <v>0</v>
@@ -11643,11 +11631,11 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>예원예술대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="D510" t="n">
         <v>0</v>
@@ -11665,11 +11653,11 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>대구예술대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D511" t="n">
         <v>0</v>
@@ -11687,11 +11675,11 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D512" t="n">
         <v>0</v>
@@ -11709,11 +11697,11 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>금강대학교</t>
+          <t>예원예술대학교</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D513" t="n">
         <v>0</v>
@@ -14415,11 +14403,11 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>서울기독대학교</t>
+          <t>금강대학교</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D636" t="n">
         <v>0</v>
@@ -14437,11 +14425,11 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>금강대학교</t>
+          <t>대구예술대학교</t>
         </is>
       </c>
       <c r="C637" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D637" t="n">
         <v>0</v>
@@ -14459,11 +14447,11 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>대구예술대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C638" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D638" t="n">
         <v>0</v>
@@ -14481,11 +14469,11 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>예원예술대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C639" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="D639" t="n">
         <v>0</v>
@@ -14503,11 +14491,11 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C640" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D640" t="n">
         <v>0</v>
@@ -14525,11 +14513,11 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>추계예술대학교</t>
+          <t>서울기독대학교</t>
         </is>
       </c>
       <c r="C641" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="D641" t="n">
         <v>0</v>
@@ -14547,11 +14535,11 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>예원예술대학교</t>
         </is>
       </c>
       <c r="C642" t="n">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D642" t="n">
         <v>0</v>
@@ -14569,11 +14557,11 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>추계예술대학교</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="D643" t="n">
         <v>0</v>
@@ -16395,14 +16383,14 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>경성대학교</t>
+          <t>경동대학교</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>455</v>
+        <v>247</v>
       </c>
       <c r="D726" t="n">
-        <v>40.5168</v>
+        <v>21.9871</v>
       </c>
       <c r="E726" t="n">
         <v>0.089</v>
@@ -16417,14 +16405,14 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>경동대학교</t>
+          <t>경성대학교</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>247</v>
+        <v>455</v>
       </c>
       <c r="D727" t="n">
-        <v>21.9871</v>
+        <v>40.5168</v>
       </c>
       <c r="E727" t="n">
         <v>0.089</v>
@@ -17253,11 +17241,11 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>금강대학교</t>
         </is>
       </c>
       <c r="C765" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D765" t="n">
         <v>0</v>
@@ -17275,11 +17263,11 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>추계예술대학교</t>
+          <t>대구예술대학교</t>
         </is>
       </c>
       <c r="C766" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D766" t="n">
         <v>0</v>
@@ -17297,11 +17285,11 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C767" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D767" t="n">
         <v>0</v>
@@ -17319,11 +17307,11 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>금강대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C768" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D768" t="n">
         <v>0</v>
@@ -17341,11 +17329,11 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>서울기독대학교</t>
+          <t>목포가톨릭대학교</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D769" t="n">
         <v>0</v>
@@ -17385,11 +17373,11 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>총신대학교</t>
+          <t>서울기독대학교</t>
         </is>
       </c>
       <c r="C771" t="n">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="D771" t="n">
         <v>0</v>
@@ -17407,11 +17395,11 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>목포가톨릭대학교</t>
+          <t>총신대학교</t>
         </is>
       </c>
       <c r="C772" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="D772" t="n">
         <v>0</v>
@@ -17429,11 +17417,11 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>대구예술대학교</t>
+          <t>추계예술대학교</t>
         </is>
       </c>
       <c r="C773" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D773" t="n">
         <v>0</v>
@@ -18463,14 +18451,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>한서대학교</t>
+          <t>고신대학교</t>
         </is>
       </c>
       <c r="C820" t="n">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D820" t="n">
-        <v>61.0978</v>
+        <v>68.01949999999999</v>
       </c>
       <c r="E820" t="n">
         <v>0.2314</v>
@@ -18485,14 +18473,14 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>고신대학교</t>
+          <t>한서대학교</t>
         </is>
       </c>
       <c r="C821" t="n">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="D821" t="n">
-        <v>68.01949999999999</v>
+        <v>61.0978</v>
       </c>
       <c r="E821" t="n">
         <v>0.2314</v>
@@ -19915,14 +19903,14 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>한세대학교</t>
+          <t>제주국제대학교</t>
         </is>
       </c>
       <c r="C886" t="n">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="D886" t="n">
-        <v>3.75</v>
+        <v>1.8611</v>
       </c>
       <c r="E886" t="n">
         <v>0.0321</v>
@@ -19937,14 +19925,14 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>제주국제대학교</t>
+          <t>한세대학교</t>
         </is>
       </c>
       <c r="C887" t="n">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="D887" t="n">
-        <v>1.8611</v>
+        <v>3.75</v>
       </c>
       <c r="E887" t="n">
         <v>0.0321</v>
@@ -20245,11 +20233,11 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C901" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D901" t="n">
         <v>0</v>
@@ -20267,11 +20255,11 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>추계예술대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C902" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D902" t="n">
         <v>0</v>
@@ -20289,7 +20277,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>목포가톨릭대학교</t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -20311,11 +20299,11 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>서울기독대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C904" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D904" t="n">
         <v>0</v>
@@ -20333,11 +20321,11 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>한일장신대학교</t>
+          <t>서울기독대학교</t>
         </is>
       </c>
       <c r="C905" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D905" t="n">
         <v>0</v>
@@ -20355,11 +20343,11 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>추계예술대학교</t>
         </is>
       </c>
       <c r="C906" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D906" t="n">
         <v>0</v>
@@ -20377,11 +20365,11 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>목포가톨릭대학교</t>
+          <t>한일장신대학교</t>
         </is>
       </c>
       <c r="C907" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D907" t="n">
         <v>0</v>
@@ -22973,14 +22961,14 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>협성대학교</t>
+          <t>평택대학교</t>
         </is>
       </c>
       <c r="C1025" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D1025" t="n">
-        <v>2.625</v>
+        <v>2.409</v>
       </c>
       <c r="E1025" t="n">
         <v>0.0182</v>
@@ -22995,14 +22983,14 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>평택대학교</t>
+          <t>협성대학교</t>
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D1026" t="n">
-        <v>2.409</v>
+        <v>2.625</v>
       </c>
       <c r="E1026" t="n">
         <v>0.0182</v>
@@ -23127,11 +23115,11 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>대구예술대학교</t>
+          <t>금강대학교</t>
         </is>
       </c>
       <c r="C1032" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D1032" t="n">
         <v>0</v>
@@ -23149,11 +23137,11 @@
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>대구예술대학교</t>
         </is>
       </c>
       <c r="C1033" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D1033" t="n">
         <v>0</v>
@@ -23193,11 +23181,11 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>금강대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C1035" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1035" t="n">
         <v>0</v>
@@ -23215,11 +23203,11 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>예원예술대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C1036" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D1036" t="n">
         <v>0</v>
@@ -23237,11 +23225,11 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>신경주대학교</t>
+          <t>서울기독대학교</t>
         </is>
       </c>
       <c r="C1037" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D1037" t="n">
         <v>0</v>
@@ -23259,11 +23247,11 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>신경주대학교</t>
         </is>
       </c>
       <c r="C1038" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D1038" t="n">
         <v>0</v>
@@ -23281,11 +23269,11 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>한일장신대학교</t>
+          <t>예원예술대학교</t>
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D1039" t="n">
         <v>0</v>
@@ -23303,11 +23291,11 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>서울기독대학교</t>
+          <t>제주국제대학교</t>
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D1040" t="n">
         <v>0</v>
@@ -23325,11 +23313,11 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>제주국제대학교</t>
+          <t>한일장신대학교</t>
         </is>
       </c>
       <c r="C1041" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D1041" t="n">
         <v>0</v>
@@ -25151,14 +25139,14 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>세한대학교</t>
+          <t>김천대학교</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D1124" t="n">
-        <v>12.8249</v>
+        <v>9.470499999999999</v>
       </c>
       <c r="E1124" t="n">
         <v>0.09569999999999999</v>
@@ -25173,14 +25161,14 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>김천대학교</t>
+          <t>세한대학교</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="D1125" t="n">
-        <v>9.470499999999999</v>
+        <v>12.8249</v>
       </c>
       <c r="E1125" t="n">
         <v>0.09569999999999999</v>
@@ -26097,11 +26085,11 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>금강대학교</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D1167" t="n">
         <v>0</v>
@@ -26119,11 +26107,11 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>목포가톨릭대학교</t>
+          <t>대구예술대학교</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D1168" t="n">
         <v>0</v>
@@ -26141,11 +26129,11 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>추계예술대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D1169" t="n">
         <v>0</v>
@@ -26163,11 +26151,11 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D1170" t="n">
         <v>0</v>
@@ -26185,11 +26173,11 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>예원예술대학교</t>
+          <t>목포가톨릭대학교</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D1171" t="n">
         <v>0</v>
@@ -26207,11 +26195,11 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>대구예술대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1172" t="n">
         <v>0</v>
@@ -26229,11 +26217,11 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>금강대학교</t>
+          <t>신경주대학교</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D1173" t="n">
         <v>0</v>
@@ -26251,11 +26239,11 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>예원예술대학교</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D1174" t="n">
         <v>0</v>
@@ -26273,11 +26261,11 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>신경주대학교</t>
+          <t>추계예술대학교</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D1175" t="n">
         <v>0</v>
@@ -29111,11 +29099,11 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>예원예술대학교</t>
+          <t>대구예술대학교</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D1304" t="n">
         <v>0</v>
@@ -29133,11 +29121,11 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>대구예술대학교</t>
+          <t>대신대학교</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D1305" t="n">
         <v>0</v>
@@ -29155,7 +29143,7 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C1306" t="n">
@@ -29177,11 +29165,11 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>대신대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D1307" t="n">
         <v>0</v>
@@ -29199,11 +29187,11 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>한일장신대학교</t>
+          <t>예원예술대학교</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D1308" t="n">
         <v>0</v>
@@ -29221,11 +29209,11 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>한일장신대학교</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D1309" t="n">
         <v>0</v>
@@ -29252,42 +29240,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>연도</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>학교명</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>전임교원수</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SCI/SCOPUS논문수</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>1인당논문수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>권역명</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>권역순위</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>전국순위</t>
         </is>
@@ -33326,10 +33314,10 @@
         <v>803</v>
       </c>
       <c r="D136" t="n">
-        <v>251.6849</v>
+        <v>324.2749</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3134</v>
+        <v>0.4038</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -33340,7 +33328,7 @@
         <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137">
@@ -33356,10 +33344,10 @@
         <v>508</v>
       </c>
       <c r="D137" t="n">
-        <v>50.9596</v>
+        <v>72.7248</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1003</v>
+        <v>0.1432</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -33370,7 +33358,7 @@
         <v>2</v>
       </c>
       <c r="H137" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="138">
@@ -33386,10 +33374,10 @@
         <v>246</v>
       </c>
       <c r="D138" t="n">
-        <v>19.0256</v>
+        <v>31.8065</v>
       </c>
       <c r="E138" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -33400,7 +33388,7 @@
         <v>3</v>
       </c>
       <c r="H138" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="139">
@@ -33409,17 +33397,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>한라대학교</t>
+          <t>상지대학교</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="D139" t="n">
-        <v>4.3584</v>
+        <v>12.0688</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0323</v>
+        <v>0.0439</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -33430,7 +33418,7 @@
         <v>4</v>
       </c>
       <c r="H139" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="140">
@@ -33439,17 +33427,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>상지대학교</t>
+          <t>한라대학교</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>275</v>
+        <v>135</v>
       </c>
       <c r="D140" t="n">
-        <v>8.3154</v>
+        <v>4.3584</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0302</v>
+        <v>0.0323</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -33460,7 +33448,7 @@
         <v>5</v>
       </c>
       <c r="H140" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="141">
@@ -33476,10 +33464,10 @@
         <v>1437</v>
       </c>
       <c r="D141" t="n">
-        <v>1187.6728</v>
+        <v>1373.7186</v>
       </c>
       <c r="E141" t="n">
-        <v>0.8265</v>
+        <v>0.956</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -33499,17 +33487,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>고려대학교</t>
+          <t>연세대학교</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1449</v>
+        <v>1687</v>
       </c>
       <c r="D142" t="n">
-        <v>1061.4676</v>
+        <v>1446.3592</v>
       </c>
       <c r="E142" t="n">
-        <v>0.7326</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -33529,17 +33517,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>고려대학교</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1687</v>
+        <v>1449</v>
       </c>
       <c r="D143" t="n">
-        <v>1235.4901</v>
+        <v>1157.9638</v>
       </c>
       <c r="E143" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.7991</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -33566,10 +33554,10 @@
         <v>1005</v>
       </c>
       <c r="D144" t="n">
-        <v>632.2891</v>
+        <v>704.6642999999999</v>
       </c>
       <c r="E144" t="n">
-        <v>0.6291</v>
+        <v>0.7012</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -33589,17 +33577,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>건국대학교</t>
+          <t>경희대학교</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>702</v>
+        <v>1452</v>
       </c>
       <c r="D145" t="n">
-        <v>403.7162</v>
+        <v>950.2813</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.6545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -33619,17 +33607,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>경희대학교</t>
+          <t>건국대학교</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1452</v>
+        <v>702</v>
       </c>
       <c r="D146" t="n">
-        <v>781.125</v>
+        <v>457.0367</v>
       </c>
       <c r="E146" t="n">
-        <v>0.538</v>
+        <v>0.651</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -33649,17 +33637,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>한양대학교(ERICA)</t>
+          <t>중앙대학교</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>389</v>
+        <v>1043</v>
       </c>
       <c r="D147" t="n">
-        <v>204.0329</v>
+        <v>619.0765</v>
       </c>
       <c r="E147" t="n">
-        <v>0.5245</v>
+        <v>0.5936</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -33679,17 +33667,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>광운대학교</t>
+          <t>가톨릭대학교</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>330</v>
+        <v>1155</v>
       </c>
       <c r="D148" t="n">
-        <v>168.1296</v>
+        <v>654.3594000000001</v>
       </c>
       <c r="E148" t="n">
-        <v>0.5095</v>
+        <v>0.5665</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -33709,17 +33697,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>중앙대학교</t>
+          <t>한양대학교(ERICA)</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1043</v>
+        <v>389</v>
       </c>
       <c r="D149" t="n">
-        <v>527.302</v>
+        <v>217.1356</v>
       </c>
       <c r="E149" t="n">
-        <v>0.5056</v>
+        <v>0.5582</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -33739,17 +33727,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>인하대학교</t>
+          <t>아주대학교</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>835</v>
+        <v>703</v>
       </c>
       <c r="D150" t="n">
-        <v>369.9814</v>
+        <v>388.6702</v>
       </c>
       <c r="E150" t="n">
-        <v>0.4431</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -33769,17 +33757,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>가톨릭대학교</t>
+          <t>광운대학교</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1155</v>
+        <v>330</v>
       </c>
       <c r="D151" t="n">
-        <v>507.111</v>
+        <v>174.6639</v>
       </c>
       <c r="E151" t="n">
-        <v>0.4391</v>
+        <v>0.5293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -33799,17 +33787,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>아주대학교</t>
+          <t>인하대학교</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>703</v>
+        <v>835</v>
       </c>
       <c r="D152" t="n">
-        <v>307.7049</v>
+        <v>427.8538</v>
       </c>
       <c r="E152" t="n">
-        <v>0.4377</v>
+        <v>0.5124</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -33829,17 +33817,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>동국대학교</t>
+          <t>이화여자대학교</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>716</v>
+        <v>997</v>
       </c>
       <c r="D153" t="n">
-        <v>272.6429</v>
+        <v>453.4445</v>
       </c>
       <c r="E153" t="n">
-        <v>0.3808</v>
+        <v>0.4548</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -33859,17 +33847,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>숭실대학교</t>
+          <t>동국대학교</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>503</v>
+        <v>716</v>
       </c>
       <c r="D154" t="n">
-        <v>185.373</v>
+        <v>309.1728</v>
       </c>
       <c r="E154" t="n">
-        <v>0.3685</v>
+        <v>0.4318</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -33889,17 +33877,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>한국항공대학교</t>
+          <t>숭실대학교</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>163</v>
+        <v>503</v>
       </c>
       <c r="D155" t="n">
-        <v>57.7469</v>
+        <v>207.7282</v>
       </c>
       <c r="E155" t="n">
-        <v>0.3543</v>
+        <v>0.413</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -33910,7 +33898,7 @@
         <v>15</v>
       </c>
       <c r="H155" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156">
@@ -33926,10 +33914,10 @@
         <v>870</v>
       </c>
       <c r="D156" t="n">
-        <v>252.2998</v>
+        <v>350.0252</v>
       </c>
       <c r="E156" t="n">
-        <v>0.29</v>
+        <v>0.4023</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -33940,7 +33928,7 @@
         <v>16</v>
       </c>
       <c r="H156" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157">
@@ -33949,17 +33937,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>명지대학교</t>
+          <t>한국항공대학교</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>562</v>
+        <v>163</v>
       </c>
       <c r="D157" t="n">
-        <v>143.6696</v>
+        <v>60.0802</v>
       </c>
       <c r="E157" t="n">
-        <v>0.2556</v>
+        <v>0.3686</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -33970,7 +33958,7 @@
         <v>17</v>
       </c>
       <c r="H157" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="158">
@@ -33979,17 +33967,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>이화여자대학교</t>
+          <t>차의과학대학교</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>997</v>
+        <v>428</v>
       </c>
       <c r="D158" t="n">
-        <v>249.6217</v>
+        <v>136.1402</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2504</v>
+        <v>0.3181</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -34009,17 +33997,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>경기대학교</t>
+          <t>명지대학교</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>513</v>
+        <v>562</v>
       </c>
       <c r="D159" t="n">
-        <v>120.3798</v>
+        <v>165.2003</v>
       </c>
       <c r="E159" t="n">
-        <v>0.2347</v>
+        <v>0.294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -34046,10 +34034,10 @@
         <v>1106</v>
       </c>
       <c r="D160" t="n">
-        <v>254.1936</v>
+        <v>309.6258</v>
       </c>
       <c r="E160" t="n">
-        <v>0.2298</v>
+        <v>0.28</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -34069,17 +34057,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>홍익대학교</t>
+          <t>한국외국어대학교</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>747</v>
+        <v>693</v>
       </c>
       <c r="D161" t="n">
-        <v>168.1348</v>
+        <v>187.4919</v>
       </c>
       <c r="E161" t="n">
-        <v>0.2251</v>
+        <v>0.2706</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -34090,7 +34078,7 @@
         <v>21</v>
       </c>
       <c r="H161" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="162">
@@ -34099,17 +34087,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>차의과학대학교</t>
+          <t>경기대학교</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>428</v>
+        <v>513</v>
       </c>
       <c r="D162" t="n">
-        <v>90.9755</v>
+        <v>135.5845</v>
       </c>
       <c r="E162" t="n">
-        <v>0.2126</v>
+        <v>0.2643</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -34120,7 +34108,7 @@
         <v>22</v>
       </c>
       <c r="H162" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="163">
@@ -34129,17 +34117,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>한국외국어대학교</t>
+          <t>홍익대학교</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>693</v>
+        <v>747</v>
       </c>
       <c r="D163" t="n">
-        <v>137.7953</v>
+        <v>190.9705</v>
       </c>
       <c r="E163" t="n">
-        <v>0.1988</v>
+        <v>0.2556</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -34150,7 +34138,7 @@
         <v>23</v>
       </c>
       <c r="H163" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="164">
@@ -34159,17 +34147,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>국민대학교</t>
+          <t>을지대학교</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>648</v>
+        <v>393</v>
       </c>
       <c r="D164" t="n">
-        <v>113.3836</v>
+        <v>98.5779</v>
       </c>
       <c r="E164" t="n">
-        <v>0.175</v>
+        <v>0.2508</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -34180,7 +34168,7 @@
         <v>24</v>
       </c>
       <c r="H164" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="165">
@@ -34196,10 +34184,10 @@
         <v>220</v>
       </c>
       <c r="D165" t="n">
-        <v>38.0604</v>
+        <v>54.994</v>
       </c>
       <c r="E165" t="n">
-        <v>0.173</v>
+        <v>0.25</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -34210,7 +34198,7 @@
         <v>25</v>
       </c>
       <c r="H165" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="166">
@@ -34219,17 +34207,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>을지대학교</t>
+          <t>숙명여자대학교</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="D166" t="n">
-        <v>62.2359</v>
+        <v>108.2322</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1584</v>
+        <v>0.2333</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -34240,7 +34228,7 @@
         <v>26</v>
       </c>
       <c r="H166" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="167">
@@ -34249,17 +34237,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>숙명여자대학교</t>
+          <t>국민대학교</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>464</v>
+        <v>648</v>
       </c>
       <c r="D167" t="n">
-        <v>72.1692</v>
+        <v>133.5011</v>
       </c>
       <c r="E167" t="n">
-        <v>0.1555</v>
+        <v>0.206</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -34270,7 +34258,7 @@
         <v>27</v>
       </c>
       <c r="H167" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="168">
@@ -34279,17 +34267,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>한성대학교</t>
+          <t>덕성여자대학교</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="D168" t="n">
-        <v>32.2249</v>
+        <v>35.9768</v>
       </c>
       <c r="E168" t="n">
-        <v>0.1254</v>
+        <v>0.1845</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -34300,7 +34288,7 @@
         <v>28</v>
       </c>
       <c r="H168" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169">
@@ -34309,17 +34297,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>상명대학교</t>
+          <t>성신여자대학교</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>475</v>
+        <v>333</v>
       </c>
       <c r="D169" t="n">
-        <v>52.28529999999999</v>
+        <v>50.1347</v>
       </c>
       <c r="E169" t="n">
-        <v>0.1101</v>
+        <v>0.1506</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -34330,7 +34318,7 @@
         <v>29</v>
       </c>
       <c r="H169" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="170">
@@ -34339,17 +34327,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>성결대학교</t>
+          <t>서울여자대학교</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="D170" t="n">
-        <v>20.8036</v>
+        <v>34.1238</v>
       </c>
       <c r="E170" t="n">
-        <v>0.103</v>
+        <v>0.1416</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -34360,7 +34348,7 @@
         <v>30</v>
       </c>
       <c r="H170" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="171">
@@ -34369,17 +34357,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>서울여자대학교</t>
+          <t>상명대학교</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>241</v>
+        <v>475</v>
       </c>
       <c r="D171" t="n">
-        <v>22.9832</v>
+        <v>65.25829999999999</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0954</v>
+        <v>0.1374</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -34390,7 +34378,7 @@
         <v>31</v>
       </c>
       <c r="H171" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="172">
@@ -34399,17 +34387,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>덕성여자대학교</t>
+          <t>한성대학교</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>195</v>
+        <v>257</v>
       </c>
       <c r="D172" t="n">
-        <v>18.1498</v>
+        <v>33.7011</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0931</v>
+        <v>0.1311</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -34420,7 +34408,7 @@
         <v>32</v>
       </c>
       <c r="H172" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="173">
@@ -34429,17 +34417,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>성신여자대학교</t>
+          <t>경동대학교</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>333</v>
+        <v>246</v>
       </c>
       <c r="D173" t="n">
-        <v>29.4283</v>
+        <v>31.8065</v>
       </c>
       <c r="E173" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -34450,7 +34438,7 @@
         <v>33</v>
       </c>
       <c r="H173" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="174">
@@ -34459,17 +34447,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>경동대학교</t>
+          <t>성결대학교</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>246</v>
+        <v>202</v>
       </c>
       <c r="D174" t="n">
-        <v>19.0256</v>
+        <v>21.5036</v>
       </c>
       <c r="E174" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1065</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -34480,7 +34468,7 @@
         <v>34</v>
       </c>
       <c r="H174" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="175">
@@ -34496,10 +34484,10 @@
         <v>400</v>
       </c>
       <c r="D175" t="n">
-        <v>26.5629</v>
+        <v>34.4945</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0664</v>
+        <v>0.0862</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -34510,7 +34498,7 @@
         <v>35</v>
       </c>
       <c r="H175" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="176">
@@ -34519,17 +34507,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>서경대학교</t>
+          <t>동덕여자대학교</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D176" t="n">
-        <v>14.6334</v>
+        <v>19.8556</v>
       </c>
       <c r="E176" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0834</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -34549,17 +34537,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>동덕여자대학교</t>
+          <t>성공회대학교</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="D177" t="n">
-        <v>15.0331</v>
+        <v>6.719</v>
       </c>
       <c r="E177" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -34570,7 +34558,7 @@
         <v>37</v>
       </c>
       <c r="H177" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="178">
@@ -34586,10 +34574,10 @@
         <v>202</v>
       </c>
       <c r="D178" t="n">
-        <v>12.5873</v>
+        <v>15.704</v>
       </c>
       <c r="E178" t="n">
-        <v>0.0623</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -34609,17 +34597,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>한신대학교</t>
+          <t>한국성서대학교</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="D179" t="n">
-        <v>10.2</v>
+        <v>3.1749</v>
       </c>
       <c r="E179" t="n">
-        <v>0.06</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -34630,7 +34618,7 @@
         <v>39</v>
       </c>
       <c r="H179" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="180">
@@ -34639,17 +34627,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>성공회대학교</t>
+          <t>한신대학교</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="D180" t="n">
-        <v>4.719</v>
+        <v>11.4</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0569</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -34660,7 +34648,7 @@
         <v>40</v>
       </c>
       <c r="H180" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="181">
@@ -34676,10 +34664,10 @@
         <v>272</v>
       </c>
       <c r="D181" t="n">
-        <v>14.7551</v>
+        <v>18.104</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0542</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -34690,7 +34678,7 @@
         <v>41</v>
       </c>
       <c r="H181" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="182">
@@ -34699,17 +34687,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>용인대학교</t>
+          <t>서경대학교</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D182" t="n">
-        <v>8.212999999999999</v>
+        <v>14.8001</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0349</v>
+        <v>0.0664</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -34729,17 +34717,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>예원예술대학교</t>
+          <t>용인대학교</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="D183" t="n">
-        <v>2.75</v>
+        <v>14.8846</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0344</v>
+        <v>0.0633</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -34759,17 +34747,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>한세대학교</t>
+          <t>강남대학교</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>132</v>
+        <v>241</v>
       </c>
       <c r="D184" t="n">
-        <v>4.5</v>
+        <v>14.7659</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0341</v>
+        <v>0.0613</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -34796,10 +34784,10 @@
         <v>201</v>
       </c>
       <c r="D185" t="n">
-        <v>6.7346</v>
+        <v>12.0157</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0335</v>
+        <v>0.0598</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -34810,7 +34798,7 @@
         <v>45</v>
       </c>
       <c r="H185" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="186">
@@ -34819,17 +34807,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>서울기독대학교</t>
+          <t>한세대학교</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0303</v>
+        <v>0.0455</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -34840,7 +34828,7 @@
         <v>46</v>
       </c>
       <c r="H186" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="187">
@@ -34849,17 +34837,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>강남대학교</t>
+          <t>협성대학교</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>241</v>
+        <v>163</v>
       </c>
       <c r="D187" t="n">
-        <v>6.2333</v>
+        <v>6.666600000000001</v>
       </c>
       <c r="E187" t="n">
-        <v>0.0259</v>
+        <v>0.0409</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -34870,7 +34858,7 @@
         <v>47</v>
       </c>
       <c r="H187" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="188">
@@ -34879,17 +34867,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>협성대학교</t>
+          <t>예원예술대학교</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="D188" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="E188" t="n">
-        <v>0.0098</v>
+        <v>0.0344</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -34900,7 +34888,7 @@
         <v>48</v>
       </c>
       <c r="H188" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="189">
@@ -34909,17 +34897,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>총신대학교</t>
+          <t>서울기독대학교</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="D189" t="n">
         <v>1</v>
       </c>
       <c r="E189" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0303</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -34930,7 +34918,7 @@
         <v>49</v>
       </c>
       <c r="H189" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="190">
@@ -34939,17 +34927,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>평택대학교</t>
+          <t>총신대학교</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4028</v>
+        <v>3.4333</v>
       </c>
       <c r="E190" t="n">
-        <v>0.0024</v>
+        <v>0.0272</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -34960,7 +34948,7 @@
         <v>50</v>
       </c>
       <c r="H190" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="191">
@@ -34969,17 +34957,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>루터대학교</t>
+          <t>평택대학교</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>1.6291</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>0.0098</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -34990,7 +34978,7 @@
         <v>51</v>
       </c>
       <c r="H191" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="192">
@@ -34999,17 +34987,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>서울신학대학교</t>
+          <t>인천가톨릭대학교</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>0.4102</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -35017,10 +35005,10 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H192" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="193">
@@ -35029,11 +35017,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>인천가톨릭대학교</t>
+          <t>루터대학교</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -35047,10 +35035,10 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H193" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="194">
@@ -35059,11 +35047,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>추계예술대학교</t>
+          <t>서울신학대학교</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -35077,10 +35065,10 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H194" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="195">
@@ -35089,11 +35077,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>한국성서대학교</t>
+          <t>추계예술대학교</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -35107,10 +35095,10 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H195" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="196">
@@ -35126,10 +35114,10 @@
         <v>281</v>
       </c>
       <c r="D196" t="n">
-        <v>311.2127</v>
+        <v>325.9733</v>
       </c>
       <c r="E196" t="n">
-        <v>1.1075</v>
+        <v>1.16</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -35156,10 +35144,10 @@
         <v>925</v>
       </c>
       <c r="D197" t="n">
-        <v>571.1994999999999</v>
+        <v>637.3619</v>
       </c>
       <c r="E197" t="n">
-        <v>0.6175</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -35186,10 +35174,10 @@
         <v>1111</v>
       </c>
       <c r="D198" t="n">
-        <v>578.9533</v>
+        <v>657.2491</v>
       </c>
       <c r="E198" t="n">
-        <v>0.5211</v>
+        <v>0.5916</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -35216,10 +35204,10 @@
         <v>832</v>
       </c>
       <c r="D199" t="n">
-        <v>165.1918</v>
+        <v>199.9913</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1985</v>
+        <v>0.2404</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -35230,7 +35218,7 @@
         <v>4</v>
       </c>
       <c r="H199" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="200">
@@ -35239,17 +35227,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>계명대학교</t>
+          <t>인제대학교</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>897</v>
+        <v>994</v>
       </c>
       <c r="D200" t="n">
-        <v>167.3748</v>
+        <v>235.1166</v>
       </c>
       <c r="E200" t="n">
-        <v>0.1866</v>
+        <v>0.2365</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -35260,7 +35248,7 @@
         <v>5</v>
       </c>
       <c r="H200" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="201">
@@ -35269,17 +35257,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>대구대학교</t>
+          <t>대구가톨릭대학교</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D201" t="n">
-        <v>118.921</v>
+        <v>149.6194</v>
       </c>
       <c r="E201" t="n">
-        <v>0.1855</v>
+        <v>0.2323</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -35290,7 +35278,7 @@
         <v>6</v>
       </c>
       <c r="H201" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="202">
@@ -35299,17 +35287,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>대구가톨릭대학교</t>
+          <t>계명대학교</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>644</v>
+        <v>897</v>
       </c>
       <c r="D202" t="n">
-        <v>115.8482</v>
+        <v>207.9418</v>
       </c>
       <c r="E202" t="n">
-        <v>0.1799</v>
+        <v>0.2318</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -35320,7 +35308,7 @@
         <v>7</v>
       </c>
       <c r="H202" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="203">
@@ -35329,17 +35317,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>인제대학교</t>
+          <t>대구대학교</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>994</v>
+        <v>641</v>
       </c>
       <c r="D203" t="n">
-        <v>177.1874</v>
+        <v>139.4586</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1783</v>
+        <v>0.2176</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -35350,7 +35338,7 @@
         <v>8</v>
       </c>
       <c r="H203" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="204">
@@ -35366,10 +35354,10 @@
         <v>148</v>
       </c>
       <c r="D204" t="n">
-        <v>23.6801</v>
+        <v>31.1409</v>
       </c>
       <c r="E204" t="n">
-        <v>0.16</v>
+        <v>0.2104</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -35380,7 +35368,7 @@
         <v>9</v>
       </c>
       <c r="H204" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="205">
@@ -35396,10 +35384,10 @@
         <v>254</v>
       </c>
       <c r="D205" t="n">
-        <v>32.8451</v>
+        <v>40.79510000000001</v>
       </c>
       <c r="E205" t="n">
-        <v>0.1293</v>
+        <v>0.1606</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -35410,7 +35398,7 @@
         <v>10</v>
       </c>
       <c r="H205" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="206">
@@ -35426,10 +35414,10 @@
         <v>314</v>
       </c>
       <c r="D206" t="n">
-        <v>32.407</v>
+        <v>49.1983</v>
       </c>
       <c r="E206" t="n">
-        <v>0.1032</v>
+        <v>0.1567</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -35440,7 +35428,7 @@
         <v>11</v>
       </c>
       <c r="H206" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="207">
@@ -35456,10 +35444,10 @@
         <v>456</v>
       </c>
       <c r="D207" t="n">
-        <v>46.2462</v>
+        <v>62.1075</v>
       </c>
       <c r="E207" t="n">
-        <v>0.1014</v>
+        <v>0.1362</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -35470,7 +35458,7 @@
         <v>12</v>
       </c>
       <c r="H207" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="208">
@@ -35486,10 +35474,10 @@
         <v>262</v>
       </c>
       <c r="D208" t="n">
-        <v>25.759</v>
+        <v>31.3541</v>
       </c>
       <c r="E208" t="n">
-        <v>0.0983</v>
+        <v>0.1197</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -35500,7 +35488,7 @@
         <v>13</v>
       </c>
       <c r="H208" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="209">
@@ -35509,17 +35497,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>김천대학교</t>
+          <t>동명대학교</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>156</v>
+        <v>281</v>
       </c>
       <c r="D209" t="n">
-        <v>13.8609</v>
+        <v>32.0051</v>
       </c>
       <c r="E209" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1139</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -35530,7 +35518,7 @@
         <v>14</v>
       </c>
       <c r="H209" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="210">
@@ -35539,17 +35527,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>한동대학교</t>
+          <t>김천대학교</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D210" t="n">
-        <v>12.8854</v>
+        <v>17.2021</v>
       </c>
       <c r="E210" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.1103</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -35560,7 +35548,7 @@
         <v>15</v>
       </c>
       <c r="H210" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="211">
@@ -35569,17 +35557,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>위덕대학교</t>
+          <t>신라대학교</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>131</v>
+        <v>349</v>
       </c>
       <c r="D211" t="n">
-        <v>10.3352</v>
+        <v>35.8491</v>
       </c>
       <c r="E211" t="n">
-        <v>0.0789</v>
+        <v>0.1027</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -35590,7 +35578,7 @@
         <v>16</v>
       </c>
       <c r="H211" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="212">
@@ -35599,17 +35587,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>신라대학교</t>
+          <t>한동대학교</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>349</v>
+        <v>149</v>
       </c>
       <c r="D212" t="n">
-        <v>26.4147</v>
+        <v>15.0632</v>
       </c>
       <c r="E212" t="n">
-        <v>0.0757</v>
+        <v>0.1011</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -35620,7 +35608,7 @@
         <v>17</v>
       </c>
       <c r="H212" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="213">
@@ -35629,17 +35617,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>동명대학교</t>
+          <t>위덕대학교</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="D213" t="n">
-        <v>19.4132</v>
+        <v>10.3352</v>
       </c>
       <c r="E213" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0789</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -35650,7 +35638,7 @@
         <v>18</v>
       </c>
       <c r="H213" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="214">
@@ -35666,10 +35654,10 @@
         <v>451</v>
       </c>
       <c r="D214" t="n">
-        <v>30.298</v>
+        <v>34.6904</v>
       </c>
       <c r="E214" t="n">
-        <v>0.0672</v>
+        <v>0.0769</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -35680,7 +35668,7 @@
         <v>19</v>
       </c>
       <c r="H214" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="215">
@@ -35689,17 +35677,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>동의대학교</t>
+          <t>동서대학교</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>583</v>
+        <v>357</v>
       </c>
       <c r="D215" t="n">
-        <v>34.9256</v>
+        <v>26.5541</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0599</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -35710,7 +35698,7 @@
         <v>20</v>
       </c>
       <c r="H215" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="216">
@@ -35719,17 +35707,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>동서대학교</t>
+          <t>동의대학교</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>357</v>
+        <v>583</v>
       </c>
       <c r="D216" t="n">
-        <v>17.5383</v>
+        <v>41.9412</v>
       </c>
       <c r="E216" t="n">
-        <v>0.0491</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -35740,7 +35728,7 @@
         <v>21</v>
       </c>
       <c r="H216" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="217">
@@ -35756,10 +35744,10 @@
         <v>250</v>
       </c>
       <c r="D217" t="n">
-        <v>10.1512</v>
+        <v>16.0151</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0406</v>
+        <v>0.0641</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -35770,7 +35758,7 @@
         <v>22</v>
       </c>
       <c r="H217" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="218">
@@ -35779,17 +35767,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>가야대학교</t>
+          <t>동양대학교</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="D218" t="n">
-        <v>3.4</v>
+        <v>8.487299999999999</v>
       </c>
       <c r="E218" t="n">
-        <v>0.0358</v>
+        <v>0.0534</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -35800,7 +35788,7 @@
         <v>23</v>
       </c>
       <c r="H218" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="219">
@@ -35809,17 +35797,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>동양대학교</t>
+          <t>가야대학교</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="D219" t="n">
-        <v>5.544</v>
+        <v>5</v>
       </c>
       <c r="E219" t="n">
-        <v>0.0349</v>
+        <v>0.0526</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -35830,7 +35818,7 @@
         <v>24</v>
       </c>
       <c r="H219" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="220">
@@ -35846,10 +35834,10 @@
         <v>82</v>
       </c>
       <c r="D220" t="n">
-        <v>1.8953</v>
+        <v>2.8953</v>
       </c>
       <c r="E220" t="n">
-        <v>0.0231</v>
+        <v>0.0353</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -35860,7 +35848,7 @@
         <v>25</v>
       </c>
       <c r="H220" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="221">
@@ -35876,10 +35864,10 @@
         <v>210</v>
       </c>
       <c r="D221" t="n">
-        <v>3.5611</v>
+        <v>6.5651</v>
       </c>
       <c r="E221" t="n">
-        <v>0.017</v>
+        <v>0.0313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -35890,7 +35878,7 @@
         <v>26</v>
       </c>
       <c r="H221" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="222">
@@ -35906,10 +35894,10 @@
         <v>290</v>
       </c>
       <c r="D222" t="n">
-        <v>3.8667</v>
+        <v>4.3667</v>
       </c>
       <c r="E222" t="n">
-        <v>0.0133</v>
+        <v>0.0151</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -35920,7 +35908,7 @@
         <v>27</v>
       </c>
       <c r="H222" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="223">
@@ -35950,7 +35938,7 @@
         <v>28</v>
       </c>
       <c r="H223" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="224">
@@ -35980,7 +35968,7 @@
         <v>29</v>
       </c>
       <c r="H224" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="225">
@@ -36010,7 +35998,7 @@
         <v>29</v>
       </c>
       <c r="H225" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="226">
@@ -36040,7 +36028,7 @@
         <v>29</v>
       </c>
       <c r="H226" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="227">
@@ -36056,10 +36044,10 @@
         <v>86</v>
       </c>
       <c r="D227" t="n">
-        <v>0.2666</v>
+        <v>0.4666</v>
       </c>
       <c r="E227" t="n">
-        <v>0.0031</v>
+        <v>0.0054</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -36070,7 +36058,7 @@
         <v>1</v>
       </c>
       <c r="H227" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="228">
@@ -36086,10 +36074,10 @@
         <v>483</v>
       </c>
       <c r="D228" t="n">
-        <v>153.5799</v>
+        <v>205.3335</v>
       </c>
       <c r="E228" t="n">
-        <v>0.318</v>
+        <v>0.4251</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -36100,7 +36088,7 @@
         <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="229">
@@ -36116,10 +36104,10 @@
         <v>183</v>
       </c>
       <c r="D229" t="n">
-        <v>57.3918</v>
+        <v>58.2918</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3136</v>
+        <v>0.3185</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -36130,7 +36118,7 @@
         <v>2</v>
       </c>
       <c r="H229" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230">
@@ -36146,10 +36134,10 @@
         <v>271</v>
       </c>
       <c r="D230" t="n">
-        <v>67.5172</v>
+        <v>83.2881</v>
       </c>
       <c r="E230" t="n">
-        <v>0.2491</v>
+        <v>0.3073</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -36160,7 +36148,7 @@
         <v>3</v>
       </c>
       <c r="H230" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="231">
@@ -36169,17 +36157,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>선문대학교</t>
+          <t>한서대학교</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>340</v>
+        <v>266</v>
       </c>
       <c r="D231" t="n">
-        <v>78.8456</v>
+        <v>76.48949999999999</v>
       </c>
       <c r="E231" t="n">
-        <v>0.2319</v>
+        <v>0.2876</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -36199,17 +36187,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>한서대학교</t>
+          <t>선문대학교</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>266</v>
+        <v>340</v>
       </c>
       <c r="D232" t="n">
-        <v>61.5717</v>
+        <v>95.31180000000001</v>
       </c>
       <c r="E232" t="n">
-        <v>0.2315</v>
+        <v>0.2803</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -36236,10 +36224,10 @@
         <v>1106</v>
       </c>
       <c r="D233" t="n">
-        <v>254.1936</v>
+        <v>309.6258</v>
       </c>
       <c r="E233" t="n">
-        <v>0.2298</v>
+        <v>0.28</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -36259,17 +36247,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>홍익대학교</t>
+          <t>남서울대학교</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>747</v>
+        <v>349</v>
       </c>
       <c r="D234" t="n">
-        <v>168.1348</v>
+        <v>96.1628</v>
       </c>
       <c r="E234" t="n">
-        <v>0.2251</v>
+        <v>0.2755</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -36289,17 +36277,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>순천향대학교</t>
+          <t>홍익대학교</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>900</v>
+        <v>747</v>
       </c>
       <c r="D235" t="n">
-        <v>178.8471</v>
+        <v>190.9705</v>
       </c>
       <c r="E235" t="n">
-        <v>0.1987</v>
+        <v>0.2556</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -36319,17 +36307,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>남서울대학교</t>
+          <t>순천향대학교</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>349</v>
+        <v>900</v>
       </c>
       <c r="D236" t="n">
-        <v>64.69370000000001</v>
+        <v>228.5747</v>
       </c>
       <c r="E236" t="n">
-        <v>0.1854</v>
+        <v>0.254</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -36340,7 +36328,7 @@
         <v>9</v>
       </c>
       <c r="H236" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="237">
@@ -36349,17 +36337,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>중원대학교</t>
+          <t>을지대학교</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>158</v>
+        <v>393</v>
       </c>
       <c r="D237" t="n">
-        <v>28.3797</v>
+        <v>98.5779</v>
       </c>
       <c r="E237" t="n">
-        <v>0.1796</v>
+        <v>0.2508</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -36370,7 +36358,7 @@
         <v>10</v>
       </c>
       <c r="H237" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="238">
@@ -36379,17 +36367,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>을지대학교</t>
+          <t>중원대학교</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>393</v>
+        <v>158</v>
       </c>
       <c r="D238" t="n">
-        <v>62.2359</v>
+        <v>39.1305</v>
       </c>
       <c r="E238" t="n">
-        <v>0.1584</v>
+        <v>0.2477</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -36400,7 +36388,7 @@
         <v>11</v>
       </c>
       <c r="H238" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="239">
@@ -36409,17 +36397,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>청주대학교</t>
+          <t>한남대학교</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="D239" t="n">
-        <v>63.4454</v>
+        <v>86.78700000000001</v>
       </c>
       <c r="E239" t="n">
-        <v>0.1567</v>
+        <v>0.2023</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -36430,7 +36418,7 @@
         <v>12</v>
       </c>
       <c r="H239" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="240">
@@ -36439,17 +36427,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>한남대학교</t>
+          <t>청주대학교</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="D240" t="n">
-        <v>67.0309</v>
+        <v>78.92319999999999</v>
       </c>
       <c r="E240" t="n">
-        <v>0.1562</v>
+        <v>0.1949</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -36460,7 +36448,7 @@
         <v>13</v>
       </c>
       <c r="H240" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="241">
@@ -36476,10 +36464,10 @@
         <v>286</v>
       </c>
       <c r="D241" t="n">
-        <v>37.7952</v>
+        <v>54.5225</v>
       </c>
       <c r="E241" t="n">
-        <v>0.1322</v>
+        <v>0.1906</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -36506,10 +36494,10 @@
         <v>477</v>
       </c>
       <c r="D242" t="n">
-        <v>61.4167</v>
+        <v>77.3614</v>
       </c>
       <c r="E242" t="n">
-        <v>0.1288</v>
+        <v>0.1622</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -36529,17 +36517,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>상명대학교</t>
+          <t>건양대학교</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>475</v>
+        <v>396</v>
       </c>
       <c r="D243" t="n">
-        <v>52.28529999999999</v>
+        <v>56.72340000000001</v>
       </c>
       <c r="E243" t="n">
-        <v>0.1101</v>
+        <v>0.1432</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -36550,7 +36538,7 @@
         <v>16</v>
       </c>
       <c r="H243" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="244">
@@ -36559,17 +36547,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>우송대학교</t>
+          <t>상명대학교</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>332</v>
+        <v>475</v>
       </c>
       <c r="D244" t="n">
-        <v>34.3871</v>
+        <v>65.25829999999999</v>
       </c>
       <c r="E244" t="n">
-        <v>0.1036</v>
+        <v>0.1374</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -36580,7 +36568,7 @@
         <v>17</v>
       </c>
       <c r="H244" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="245">
@@ -36589,17 +36577,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>중부대학교</t>
+          <t>서원대학교</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="D245" t="n">
-        <v>29.1306</v>
+        <v>32.2172</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0998</v>
+        <v>0.1284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -36610,7 +36598,7 @@
         <v>18</v>
       </c>
       <c r="H245" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="246">
@@ -36619,17 +36607,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>건양대학교</t>
+          <t>우송대학교</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>396</v>
+        <v>332</v>
       </c>
       <c r="D246" t="n">
-        <v>37.9908</v>
+        <v>42.4288</v>
       </c>
       <c r="E246" t="n">
-        <v>0.0959</v>
+        <v>0.1278</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -36640,7 +36628,7 @@
         <v>19</v>
       </c>
       <c r="H246" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="247">
@@ -36656,10 +36644,10 @@
         <v>147</v>
       </c>
       <c r="D247" t="n">
-        <v>13.6222</v>
+        <v>17.8985</v>
       </c>
       <c r="E247" t="n">
-        <v>0.0927</v>
+        <v>0.1218</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -36670,7 +36658,7 @@
         <v>20</v>
       </c>
       <c r="H247" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="248">
@@ -36679,17 +36667,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>목원대학교</t>
+          <t>중부대학교</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D248" t="n">
-        <v>26.0452</v>
+        <v>35.2568</v>
       </c>
       <c r="E248" t="n">
-        <v>0.0871</v>
+        <v>0.1207</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -36700,7 +36688,7 @@
         <v>21</v>
       </c>
       <c r="H248" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="249">
@@ -36709,17 +36697,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>배재대학교</t>
+          <t>목원대학교</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="D249" t="n">
-        <v>23.984</v>
+        <v>33.7118</v>
       </c>
       <c r="E249" t="n">
-        <v>0.074</v>
+        <v>0.1127</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -36730,7 +36718,7 @@
         <v>22</v>
       </c>
       <c r="H249" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="250">
@@ -36739,17 +36727,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>서원대학교</t>
+          <t>배재대학교</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="D250" t="n">
-        <v>18.5172</v>
+        <v>34.6495</v>
       </c>
       <c r="E250" t="n">
-        <v>0.0738</v>
+        <v>0.1069</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -36760,7 +36748,7 @@
         <v>23</v>
       </c>
       <c r="H250" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="251">
@@ -36776,10 +36764,10 @@
         <v>361</v>
       </c>
       <c r="D251" t="n">
-        <v>23.9071</v>
+        <v>33.9757</v>
       </c>
       <c r="E251" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0941</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -36790,7 +36778,7 @@
         <v>24</v>
       </c>
       <c r="H251" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="252">
@@ -36806,10 +36794,10 @@
         <v>139</v>
       </c>
       <c r="D252" t="n">
-        <v>9.0914</v>
+        <v>12.128</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0654</v>
+        <v>0.0873</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -36820,7 +36808,7 @@
         <v>25</v>
       </c>
       <c r="H252" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="253">
@@ -36836,10 +36824,10 @@
         <v>499</v>
       </c>
       <c r="D253" t="n">
-        <v>15.6537</v>
+        <v>36.8491</v>
       </c>
       <c r="E253" t="n">
-        <v>0.0314</v>
+        <v>0.0738</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -36850,7 +36838,7 @@
         <v>26</v>
       </c>
       <c r="H253" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="254">
@@ -36866,10 +36854,10 @@
         <v>193</v>
       </c>
       <c r="D254" t="n">
-        <v>5.6394</v>
+        <v>8.898199999999999</v>
       </c>
       <c r="E254" t="n">
-        <v>0.0292</v>
+        <v>0.0461</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -36880,7 +36868,7 @@
         <v>27</v>
       </c>
       <c r="H254" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="255">
@@ -36910,7 +36898,7 @@
         <v>28</v>
       </c>
       <c r="H255" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="256">
@@ -36926,10 +36914,10 @@
         <v>818</v>
       </c>
       <c r="D256" t="n">
-        <v>202.2195</v>
+        <v>252.3125</v>
       </c>
       <c r="E256" t="n">
-        <v>0.2472</v>
+        <v>0.3085</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -36940,7 +36928,7 @@
         <v>1</v>
       </c>
       <c r="H256" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="257">
@@ -36949,17 +36937,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>원광대학교</t>
+          <t>전주대학교</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>753</v>
+        <v>380</v>
       </c>
       <c r="D257" t="n">
-        <v>88.2385</v>
+        <v>59.0145</v>
       </c>
       <c r="E257" t="n">
-        <v>0.1172</v>
+        <v>0.1553</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -36970,7 +36958,7 @@
         <v>2</v>
       </c>
       <c r="H257" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="258">
@@ -36979,17 +36967,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>세한대학교</t>
+          <t>원광대학교</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>146</v>
+        <v>753</v>
       </c>
       <c r="D258" t="n">
-        <v>14.481</v>
+        <v>114.1152</v>
       </c>
       <c r="E258" t="n">
-        <v>0.0992</v>
+        <v>0.1515</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -37000,7 +36988,7 @@
         <v>3</v>
       </c>
       <c r="H258" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="259">
@@ -37009,17 +36997,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>전주대학교</t>
+          <t>세한대학교</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>380</v>
+        <v>146</v>
       </c>
       <c r="D259" t="n">
-        <v>30.2026</v>
+        <v>18.0921</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0795</v>
+        <v>0.1239</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -37030,7 +37018,7 @@
         <v>4</v>
       </c>
       <c r="H259" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="260">
@@ -37039,17 +37027,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>동신대학교</t>
+          <t>예수대학교</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>281</v>
+        <v>23</v>
       </c>
       <c r="D260" t="n">
-        <v>20.7176</v>
+        <v>2.2667</v>
       </c>
       <c r="E260" t="n">
-        <v>0.0737</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -37069,17 +37057,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>남부대학교</t>
+          <t>동신대학교</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>123</v>
+        <v>281</v>
       </c>
       <c r="D261" t="n">
-        <v>7.7141</v>
+        <v>24.5223</v>
       </c>
       <c r="E261" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0873</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -37090,7 +37078,7 @@
         <v>6</v>
       </c>
       <c r="H261" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="262">
@@ -37099,17 +37087,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>우석대학교</t>
+          <t>남부대학교</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>266</v>
+        <v>123</v>
       </c>
       <c r="D262" t="n">
-        <v>14.0343</v>
+        <v>9.657</v>
       </c>
       <c r="E262" t="n">
-        <v>0.0528</v>
+        <v>0.0785</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -37120,7 +37108,7 @@
         <v>7</v>
       </c>
       <c r="H262" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="263">
@@ -37129,17 +37117,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>광주대학교</t>
+          <t>우석대학교</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D263" t="n">
-        <v>11.3014</v>
+        <v>20.287</v>
       </c>
       <c r="E263" t="n">
-        <v>0.0448</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -37150,7 +37138,7 @@
         <v>8</v>
       </c>
       <c r="H263" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="264">
@@ -37159,17 +37147,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>예원예술대학교</t>
+          <t>광주여자대학교</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D264" t="n">
-        <v>2.75</v>
+        <v>8.7906</v>
       </c>
       <c r="E264" t="n">
-        <v>0.0344</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -37180,7 +37168,7 @@
         <v>9</v>
       </c>
       <c r="H264" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="265">
@@ -37189,17 +37177,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>초당대학교</t>
+          <t>광주대학교</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="D265" t="n">
-        <v>2.4096</v>
+        <v>15.282</v>
       </c>
       <c r="E265" t="n">
-        <v>0.0223</v>
+        <v>0.0606</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -37210,7 +37198,7 @@
         <v>10</v>
       </c>
       <c r="H265" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="266">
@@ -37219,17 +37207,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>광주여자대학교</t>
+          <t>초당대학교</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="D266" t="n">
-        <v>2.8858</v>
+        <v>3.8429</v>
       </c>
       <c r="E266" t="n">
-        <v>0.0219</v>
+        <v>0.0356</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -37240,7 +37228,7 @@
         <v>11</v>
       </c>
       <c r="H266" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="267">
@@ -37249,17 +37237,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>한일장신대학교</t>
+          <t>예원예술대학교</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="D267" t="n">
-        <v>0.4</v>
+        <v>2.75</v>
       </c>
       <c r="E267" t="n">
-        <v>0.0089</v>
+        <v>0.0344</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -37270,7 +37258,7 @@
         <v>12</v>
       </c>
       <c r="H267" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="268">
@@ -37279,17 +37267,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>목포가톨릭대학교</t>
+          <t>한일장신대학교</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D268" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E268" t="n">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -37300,7 +37288,7 @@
         <v>13</v>
       </c>
       <c r="H268" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="269">
@@ -37309,11 +37297,11 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>예수대학교</t>
+          <t>목포가톨릭대학교</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D269" t="n">
         <v>0</v>
@@ -37327,10 +37315,10 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H269" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="270">

--- a/output/전임교원_연구실적_전처리결과.xlsx
+++ b/output/전임교원_연구실적_전처리결과.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1309"/>
+  <dimension ref="A1:F1442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29223,6 +29223,2932 @@
       </c>
       <c r="F1309" t="n">
         <v>128</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>포항공과대학교</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>294</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>357.1712</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>1.2149</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>영남대학교</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>858</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>1030.3609</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>1.2009</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>성균관대학교</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>1554</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>1636.3627</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>연세대학교</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>1632.0998</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>가천대학교</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>858.1541</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>고려대학교</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>1657</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>1376.8741</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>0.8309</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>한양대학교</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>1107</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>871.3792</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>0.7872</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>동국대학교</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>681</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>517.9674</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>경희대학교</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>1424</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>1054.7995</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>0.7407</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>건국대학교</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>646</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>465.2249</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>0.7202</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>중앙대학교</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>1192</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>848.6812000000001</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>아주대학교</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>757</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>521.9426</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>0.6895</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>한국기술교육대학교</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>186</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>127.952</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>0.6879</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>한양대학교(ERICA)</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>421</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>285.4362</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>846.6943</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>인하대학교</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>888</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>516.2642</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>울산대학교</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>1083</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>594.2994</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>이화여자대학교</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>973</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>524.9367</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>0.5395</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>광운대학교</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>296</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>152.9819</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>0.5168</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>숭실대학교</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>544</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>279.9253</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>국민대학교</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>662</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>323.0994</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>0.4881</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>연세대학교(미래)</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>406</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>192.1359</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>한국항공대학교</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>168</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>73.33759999999999</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>단국대학교</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>981</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>419.9609</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>고려대학교(세종)</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>260</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>105.4773</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>순천향대학교</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>931</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>368.7722</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>한림대학교</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>690</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>271.7633</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>조선대학교</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>730</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>275.3343</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>경기대학교</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>480</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>178.3553</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>계명대학교</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>780</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>285.4323</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>건국대학교(글로컬)</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>419</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>147.0501</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>홍익대학교</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>751</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>251.36</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>숙명여자대학교</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>422</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>140.8126</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>동국대학교(WISE)</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>293</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>97.45569999999999</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>성신여자대학교</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>330</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>105.8307</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>인제대학교</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>787</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>246.4177</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>예수대학교</t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>6.1596</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>동아대학교</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>711</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>215.4385</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>삼육대학교</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>187</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>54.2254</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>우송대학교</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>319</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>88.72880000000001</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>상명대학교</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>414</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>113.8143</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>을지대학교</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>425</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>109.4075</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>선문대학교</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>276</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>69.32250000000001</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>덕성여자대학교</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>194</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>46.3865</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>차의과학대학교</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>504</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>120.2407</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>0.2386</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>전주대학교</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>323</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>75.7812</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>명지대학교</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>495</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>111.4928</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>한서대학교</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>221</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>49.4499</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>0.2238</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>대진대학교</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>229</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>49.3833</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>한국외국어대학교</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>606</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>128.1155</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>0.2114</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>원광대학교</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>733</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>151.2914</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>한국공학대학교</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>263</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>52.5493</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>건양대학교</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>341</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>65.422</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>서울여자대학교</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>230</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>42.583</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>한남대학교</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>369</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>65.7175</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>0.1781</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>동양대학교</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>131</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>22.5965</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>부산가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>118</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>20.3414</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>동의대학교</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>536</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>90.19589999999999</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>0.1683</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>세한대학교</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>102</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>17.1549</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>청주대학교</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>422</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>69.45480000000001</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>0.1646</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>대구대학교</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>485</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>79.56359999999999</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>동덕여자대학교</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>213</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>33.5589</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>한동대학교</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>151</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>23.6001</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>대구가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>526</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>가톨릭관동대학교</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>338</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>49.6114</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>세명대학교</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>224</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>32.196</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>동신대학교</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>252</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>36.0812</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>가톨릭꽃동네대학교</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>우석대학교</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>249</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>34.3209</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>성공회대학교</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>85</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>11.0549</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>호서대학교</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>406</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>52.6547</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>강남대학교</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>195</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>24.5689</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>동서대학교</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>304</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>38.2638</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>중부대학교</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>326</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>0.1251</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>경남대학교</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>356</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>44.1644</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>화성의과학대학교</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>3.6465</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>중원대학교</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>119</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>14.1753</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>동명대학교</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>222</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>26.3878</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>0.1189</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>상지대학교</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>228</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>26.918</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>고신대학교</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>240</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>27.6597</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>대전대학교</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>264</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>30.2593</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>수원대학교</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>322</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>35.2778</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>경일대학교</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>241</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>26.3145</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>경성대학교</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>398</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>43.3087</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>극동대학교</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>117</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>12.6785</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>신라대학교</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>256</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>가야대학교</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>5.9611</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>창신대학교</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>영산대학교</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>185</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>17.6324</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="F1398" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>용인대학교</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>185</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>17.4885</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="F1399" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>경동대학교</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>244</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>21.4547</v>
+      </c>
+      <c r="E1400" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="F1400" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>신한대학교</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>263</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>23.1254</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="F1401" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>남서울대학교</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>308</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>26.5496</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="F1402" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>한라대학교</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>97</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>8.2417</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F1403" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>평택대학교</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>113</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>9.5213</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="F1404" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>안양대학교</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>170</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>14.1078</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F1405" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>김천대학교</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>98</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>8.0884</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="F1406" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>한성대학교</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>279</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>22.8511</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="F1407" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>목원대학교</t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>257</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>20.897</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="F1408" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>남부대학교</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>101</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>8.154400000000001</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>0.08069999999999999</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>배재대학교</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>240</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>19.3391</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>0.0806</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>광주대학교</t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>187</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>14.7975</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="F1411" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>광주여자대학교</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
+        <v>121</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>9.4147</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>0.07779999999999999</v>
+      </c>
+      <c r="F1412" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>서원대학교</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>222</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>17.025</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="F1413" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>대구한의대학교</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>222</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="F1414" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>경운대학교</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>195</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>14.2042</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>한신대학교</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>170</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>12.0762</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>강서대학교</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>3.599</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>백석대학교</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>445</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>26.9092</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>서경대학교</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>246</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>14.7159</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>한세대학교</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>98</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>4.9667</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>부산외국어대학교</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>207</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>7.6286</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>서울신학대학교</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>95</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>3.4106</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>위덕대학교</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>2.6548</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>협성대학교</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>121</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>4.0072</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>성결대학교</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>165</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>5.1333</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>나사렛대학교</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>147</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>3.975</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>루터대학교</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="F1427" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>한국성서대학교</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>40</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>초당대학교</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>92</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>총신대학교</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>104</v>
+      </c>
+      <c r="D1430" t="n">
+        <v>1.6429</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>인천가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>서울기독대학교</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>0.7111</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>유원대학교</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>1.0834</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>목포가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>금강대학교</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>대구예술대학교</t>
+        </is>
+      </c>
+      <c r="C1436" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>대신대학교</t>
+        </is>
+      </c>
+      <c r="C1437" t="n">
+        <v>67</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>부산장신대학교</t>
+        </is>
+      </c>
+      <c r="C1438" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>신경주대학교</t>
+        </is>
+      </c>
+      <c r="C1439" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>예원예술대학교</t>
+        </is>
+      </c>
+      <c r="C1440" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>추계예술대학교</t>
+        </is>
+      </c>
+      <c r="C1441" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>한일장신대학교</t>
+        </is>
+      </c>
+      <c r="C1442" t="n">
+        <v>35</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -29236,7 +32162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1369"/>
+  <dimension ref="A1:H1508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70321,6 +73247,4176 @@
         <v>128</v>
       </c>
     </row>
+    <row r="1370">
+      <c r="A1370" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>연세대학교(미래)</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>406</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>192.1359</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>강원권</t>
+        </is>
+      </c>
+      <c r="G1370" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1370" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>한림대학교</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>690</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>271.7633</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>강원권</t>
+        </is>
+      </c>
+      <c r="G1371" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1371" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>가톨릭관동대학교</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>338</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>49.6114</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>강원권</t>
+        </is>
+      </c>
+      <c r="G1372" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1372" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>상지대학교</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>228</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>26.918</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>강원권</t>
+        </is>
+      </c>
+      <c r="G1373" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1373" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>경동대학교</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>244</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>21.4547</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>강원권</t>
+        </is>
+      </c>
+      <c r="G1374" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1374" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>한라대학교</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>97</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>8.2417</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>강원권</t>
+        </is>
+      </c>
+      <c r="G1375" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1375" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>성균관대학교</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>1554</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>1636.3627</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1376" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1376" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>연세대학교</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>1632.0998</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1377" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1377" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>가천대학교</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>858.1541</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1378" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1378" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>고려대학교</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>1657</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>1376.8741</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>0.8309</v>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1379" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1379" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>한양대학교</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>1107</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>871.3792</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>0.7872</v>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1380" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1380" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>동국대학교</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>681</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>517.9674</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>0.7606000000000001</v>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1381" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1381" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>경희대학교</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>1424</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>1054.7995</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>0.7407</v>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1382" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1382" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>건국대학교</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>646</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>465.2249</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>0.7202</v>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1383" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1383" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>중앙대학교</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>1192</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>848.6812000000001</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1384" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1384" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>아주대학교</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>757</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>521.9426</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>0.6895</v>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1385" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1385" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>한양대학교(ERICA)</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>421</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>285.4362</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1386" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1386" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>846.6943</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1387" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>인하대학교</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>888</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>516.2642</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1388" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>이화여자대학교</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>973</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>524.9367</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>0.5395</v>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1389" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>광운대학교</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>296</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>152.9819</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>0.5168</v>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1390" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>숭실대학교</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>544</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>279.9253</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1391" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1391" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>국민대학교</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>662</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>323.0994</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>0.4881</v>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1392" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>한국항공대학교</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>168</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>73.33759999999999</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1393" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1393" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>단국대학교</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>981</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>419.9609</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1394" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1394" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>경기대학교</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>480</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>178.3553</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1395" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1395" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>홍익대학교</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>751</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>251.36</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1396" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1396" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>숙명여자대학교</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>422</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>140.8126</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1397" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1397" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>성신여자대학교</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>330</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>105.8307</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1398" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1398" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>삼육대학교</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>187</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>54.2254</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1399" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1399" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>상명대학교</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>414</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>113.8143</v>
+      </c>
+      <c r="E1400" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1400" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1400" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>을지대학교</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>425</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>109.4075</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1401" t="n">
+        <v>26</v>
+      </c>
+      <c r="H1401" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>덕성여자대학교</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>194</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>46.3865</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1402" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1402" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>차의과학대학교</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>504</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>120.2407</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>0.2386</v>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1403" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1403" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>명지대학교</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>495</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>111.4928</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1404" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1404" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>대진대학교</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>229</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>49.3833</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1405" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1405" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>한국외국어대학교</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>606</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>128.1155</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>0.2114</v>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1406" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1406" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>한국공학대학교</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>263</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>52.5493</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1407" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1407" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>서울여자대학교</t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>230</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>42.583</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1408" t="n">
+        <v>33</v>
+      </c>
+      <c r="H1408" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>동덕여자대학교</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>213</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>33.5589</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1409" t="n">
+        <v>34</v>
+      </c>
+      <c r="H1409" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>성공회대학교</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>85</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>11.0549</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1410" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1410" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>강남대학교</t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>195</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>24.5689</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1411" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1411" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>화성의과학대학교</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>3.6465</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1412" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1412" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>수원대학교</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>322</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>35.2778</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1413" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1413" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>용인대학교</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>185</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>17.4885</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1414" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1414" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>경동대학교</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>244</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>21.4547</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1415" t="n">
+        <v>40</v>
+      </c>
+      <c r="H1415" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>신한대학교</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>263</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>23.1254</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1416" t="n">
+        <v>40</v>
+      </c>
+      <c r="H1416" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>평택대학교</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>113</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>9.5213</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1417" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1417" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>안양대학교</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>170</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>14.1078</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1418" t="n">
+        <v>43</v>
+      </c>
+      <c r="H1418" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>한성대학교</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>279</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>22.8511</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1419" t="n">
+        <v>44</v>
+      </c>
+      <c r="H1419" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>한신대학교</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>170</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>12.0762</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1420" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1420" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>강서대학교</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>3.599</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1421" t="n">
+        <v>46</v>
+      </c>
+      <c r="H1421" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>서경대학교</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>246</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>14.7159</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1422" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1422" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>한세대학교</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>98</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>4.9667</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1423" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1423" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>서울신학대학교</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>95</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>3.4106</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1424" t="n">
+        <v>49</v>
+      </c>
+      <c r="H1424" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>협성대학교</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>121</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>4.0072</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1425" t="n">
+        <v>50</v>
+      </c>
+      <c r="H1425" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>성결대학교</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>165</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>5.1333</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1426" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1426" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>루터대학교</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1427" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1427" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>한국성서대학교</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>40</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1428" t="n">
+        <v>53</v>
+      </c>
+      <c r="H1428" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>총신대학교</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>104</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>1.6429</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1429" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1429" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>인천가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1430" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1430" t="n">
+        <v>55</v>
+      </c>
+      <c r="H1430" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>서울기독대학교</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>0.7111</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1431" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1431" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>예원예술대학교</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1432" t="n">
+        <v>57</v>
+      </c>
+      <c r="H1432" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>추계예술대학교</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>수도권</t>
+        </is>
+      </c>
+      <c r="G1433" t="n">
+        <v>57</v>
+      </c>
+      <c r="H1433" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>포항공과대학교</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>294</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>357.1712</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>1.2149</v>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1434" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1434" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>영남대학교</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>858</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>1030.3609</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>1.2009</v>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1435" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1435" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>울산대학교</t>
+        </is>
+      </c>
+      <c r="C1436" t="n">
+        <v>1083</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>594.2994</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1436" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1436" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>계명대학교</t>
+        </is>
+      </c>
+      <c r="C1437" t="n">
+        <v>780</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>285.4323</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1437" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1437" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>동국대학교(WISE)</t>
+        </is>
+      </c>
+      <c r="C1438" t="n">
+        <v>293</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>97.45569999999999</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1438" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1438" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>인제대학교</t>
+        </is>
+      </c>
+      <c r="C1439" t="n">
+        <v>787</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>246.4177</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1439" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1439" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>동아대학교</t>
+        </is>
+      </c>
+      <c r="C1440" t="n">
+        <v>711</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>215.4385</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1440" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1440" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>동양대학교</t>
+        </is>
+      </c>
+      <c r="C1441" t="n">
+        <v>131</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>22.5965</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1441" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1441" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>부산가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1442" t="n">
+        <v>118</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>20.3414</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1442" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1442" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>동의대학교</t>
+        </is>
+      </c>
+      <c r="C1443" t="n">
+        <v>536</v>
+      </c>
+      <c r="D1443" t="n">
+        <v>90.19589999999999</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>0.1683</v>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1443" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1443" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>대구대학교</t>
+        </is>
+      </c>
+      <c r="C1444" t="n">
+        <v>485</v>
+      </c>
+      <c r="D1444" t="n">
+        <v>79.56359999999999</v>
+      </c>
+      <c r="E1444" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1444" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1444" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>한동대학교</t>
+        </is>
+      </c>
+      <c r="C1445" t="n">
+        <v>151</v>
+      </c>
+      <c r="D1445" t="n">
+        <v>23.6001</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1445" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1445" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>대구가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1446" t="n">
+        <v>526</v>
+      </c>
+      <c r="D1446" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1446" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1446" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>동서대학교</t>
+        </is>
+      </c>
+      <c r="C1447" t="n">
+        <v>304</v>
+      </c>
+      <c r="D1447" t="n">
+        <v>38.2638</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1447" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1447" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>경남대학교</t>
+        </is>
+      </c>
+      <c r="C1448" t="n">
+        <v>356</v>
+      </c>
+      <c r="D1448" t="n">
+        <v>44.1644</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1448" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1448" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>동명대학교</t>
+        </is>
+      </c>
+      <c r="C1449" t="n">
+        <v>222</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>26.3878</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>0.1189</v>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1449" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1449" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>고신대학교</t>
+        </is>
+      </c>
+      <c r="C1450" t="n">
+        <v>240</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>27.6597</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1450" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1450" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>경일대학교</t>
+        </is>
+      </c>
+      <c r="C1451" t="n">
+        <v>241</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>26.3145</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1451" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1451" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>경성대학교</t>
+        </is>
+      </c>
+      <c r="C1452" t="n">
+        <v>398</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>43.3087</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1452" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1452" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>신라대학교</t>
+        </is>
+      </c>
+      <c r="C1453" t="n">
+        <v>256</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1453" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1453" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>가야대학교</t>
+        </is>
+      </c>
+      <c r="C1454" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>5.9611</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1454" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1454" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>창신대학교</t>
+        </is>
+      </c>
+      <c r="C1455" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1455" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1455" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1455" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>영산대학교</t>
+        </is>
+      </c>
+      <c r="C1456" t="n">
+        <v>185</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>17.6324</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1456" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1456" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>김천대학교</t>
+        </is>
+      </c>
+      <c r="C1457" t="n">
+        <v>98</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>8.0884</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1457" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1457" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>대구한의대학교</t>
+        </is>
+      </c>
+      <c r="C1458" t="n">
+        <v>222</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1458" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1458" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>경운대학교</t>
+        </is>
+      </c>
+      <c r="C1459" t="n">
+        <v>195</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>14.2042</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1459" t="n">
+        <v>26</v>
+      </c>
+      <c r="H1459" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>부산외국어대학교</t>
+        </is>
+      </c>
+      <c r="C1460" t="n">
+        <v>207</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>7.6286</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1460" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1460" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>위덕대학교</t>
+        </is>
+      </c>
+      <c r="C1461" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>2.6548</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1461" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1461" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>대구예술대학교</t>
+        </is>
+      </c>
+      <c r="C1462" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1462" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>대신대학교</t>
+        </is>
+      </c>
+      <c r="C1463" t="n">
+        <v>67</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1463" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1463" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>부산장신대학교</t>
+        </is>
+      </c>
+      <c r="C1464" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1464" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1464" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>신경주대학교</t>
+        </is>
+      </c>
+      <c r="C1465" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>영남권</t>
+        </is>
+      </c>
+      <c r="G1465" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1465" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>한국기술교육대학교</t>
+        </is>
+      </c>
+      <c r="C1466" t="n">
+        <v>186</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>127.952</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>0.6879</v>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1466" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1466" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>단국대학교</t>
+        </is>
+      </c>
+      <c r="C1467" t="n">
+        <v>981</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>419.9609</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1467" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1467" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>고려대학교(세종)</t>
+        </is>
+      </c>
+      <c r="C1468" t="n">
+        <v>260</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>105.4773</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1468" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1468" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>순천향대학교</t>
+        </is>
+      </c>
+      <c r="C1469" t="n">
+        <v>931</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>368.7722</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1469" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1469" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>건국대학교(글로컬)</t>
+        </is>
+      </c>
+      <c r="C1470" t="n">
+        <v>419</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>147.0501</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1470" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1470" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>홍익대학교</t>
+        </is>
+      </c>
+      <c r="C1471" t="n">
+        <v>751</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>251.36</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1471" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1471" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>우송대학교</t>
+        </is>
+      </c>
+      <c r="C1472" t="n">
+        <v>319</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>88.72880000000001</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1472" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1472" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>상명대학교</t>
+        </is>
+      </c>
+      <c r="C1473" t="n">
+        <v>414</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>113.8143</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1473" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>을지대학교</t>
+        </is>
+      </c>
+      <c r="C1474" t="n">
+        <v>425</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>109.4075</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1474" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>선문대학교</t>
+        </is>
+      </c>
+      <c r="C1475" t="n">
+        <v>276</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>69.32250000000001</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1475" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>한서대학교</t>
+        </is>
+      </c>
+      <c r="C1476" t="n">
+        <v>221</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>49.4499</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>0.2238</v>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1476" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>건양대학교</t>
+        </is>
+      </c>
+      <c r="C1477" t="n">
+        <v>341</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>65.422</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1477" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>한남대학교</t>
+        </is>
+      </c>
+      <c r="C1478" t="n">
+        <v>369</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>65.7175</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>0.1781</v>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1478" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>청주대학교</t>
+        </is>
+      </c>
+      <c r="C1479" t="n">
+        <v>422</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>69.45480000000001</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>0.1646</v>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1479" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>세명대학교</t>
+        </is>
+      </c>
+      <c r="C1480" t="n">
+        <v>224</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>32.196</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1480" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>가톨릭꽃동네대학교</t>
+        </is>
+      </c>
+      <c r="C1481" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1481" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>호서대학교</t>
+        </is>
+      </c>
+      <c r="C1482" t="n">
+        <v>406</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>52.6547</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1482" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>중부대학교</t>
+        </is>
+      </c>
+      <c r="C1483" t="n">
+        <v>326</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>0.1251</v>
+      </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1483" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>중원대학교</t>
+        </is>
+      </c>
+      <c r="C1484" t="n">
+        <v>119</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>14.1753</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1484" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>대전대학교</t>
+        </is>
+      </c>
+      <c r="C1485" t="n">
+        <v>264</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>30.2593</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1485" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>극동대학교</t>
+        </is>
+      </c>
+      <c r="C1486" t="n">
+        <v>117</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>12.6785</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1486" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>남서울대학교</t>
+        </is>
+      </c>
+      <c r="C1487" t="n">
+        <v>308</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>26.5496</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1487" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>목원대학교</t>
+        </is>
+      </c>
+      <c r="C1488" t="n">
+        <v>257</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>20.897</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1488" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>배재대학교</t>
+        </is>
+      </c>
+      <c r="C1489" t="n">
+        <v>240</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>19.3391</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>0.0806</v>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1489" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>서원대학교</t>
+        </is>
+      </c>
+      <c r="C1490" t="n">
+        <v>222</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>17.025</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1490" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>백석대학교</t>
+        </is>
+      </c>
+      <c r="C1491" t="n">
+        <v>445</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>26.9092</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1491" t="n">
+        <v>26</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>나사렛대학교</t>
+        </is>
+      </c>
+      <c r="C1492" t="n">
+        <v>147</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>3.975</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1492" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1492" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>유원대학교</t>
+        </is>
+      </c>
+      <c r="C1493" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>1.0834</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1493" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>금강대학교</t>
+        </is>
+      </c>
+      <c r="C1494" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>충청권</t>
+        </is>
+      </c>
+      <c r="G1494" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1494" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>조선대학교</t>
+        </is>
+      </c>
+      <c r="C1495" t="n">
+        <v>730</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>275.3343</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1495" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1495" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>예수대학교</t>
+        </is>
+      </c>
+      <c r="C1496" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>6.1596</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1496" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1496" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>전주대학교</t>
+        </is>
+      </c>
+      <c r="C1497" t="n">
+        <v>323</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>75.7812</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>0.2346</v>
+      </c>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1497" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>원광대학교</t>
+        </is>
+      </c>
+      <c r="C1498" t="n">
+        <v>733</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>151.2914</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>0.2064</v>
+      </c>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1498" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>세한대학교</t>
+        </is>
+      </c>
+      <c r="C1499" t="n">
+        <v>102</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>17.1549</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1499" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>동신대학교</t>
+        </is>
+      </c>
+      <c r="C1500" t="n">
+        <v>252</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>36.0812</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1500" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>우석대학교</t>
+        </is>
+      </c>
+      <c r="C1501" t="n">
+        <v>249</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>34.3209</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1501" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>남부대학교</t>
+        </is>
+      </c>
+      <c r="C1502" t="n">
+        <v>101</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>8.154400000000001</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>0.08069999999999999</v>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1502" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>광주대학교</t>
+        </is>
+      </c>
+      <c r="C1503" t="n">
+        <v>187</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>14.7975</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1503" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>광주여자대학교</t>
+        </is>
+      </c>
+      <c r="C1504" t="n">
+        <v>121</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>9.4147</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>0.07779999999999999</v>
+      </c>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1504" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>초당대학교</t>
+        </is>
+      </c>
+      <c r="C1505" t="n">
+        <v>92</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1505" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>목포가톨릭대학교</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1506" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>예원예술대학교</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1507" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>한일장신대학교</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>35</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>호남권</t>
+        </is>
+      </c>
+      <c r="G1508" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1508" t="n">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
